--- a/pensum/ma10/MA10_Markedsplanen_oppsummert_Oppgaver_v6.xlsx
+++ b/pensum/ma10/MA10_Markedsplanen_oppsummert_Oppgaver_v6.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="218">
   <si>
     <t xml:space="preserve">Markedsplanen samlet: oppgaver til kapittel 10</t>
   </si>
@@ -65,30 +65,60 @@
     <t xml:space="preserve">Dette er øvingsmateriell til repetisjons- og øvingsstøtte. I besvarelser, caser, prosjektoppgaver og eksamen gjelder lærebøkene og oppgitte primærkilder.</t>
   </si>
   <si>
+    <t xml:space="preserve">Udifferensiert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1A: Punkt 1–4 i markedsplanen for solcelle og lading: henger de sammen?</t>
   </si>
   <si>
+    <t xml:space="preserve">Differensiert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alene, i par eller i gruppe, slik du vil.</t>
   </si>
   <si>
+    <t xml:space="preserve">Konsentrert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Situasjonen</t>
   </si>
   <si>
+    <t xml:space="preserve">Markedsinntrengning</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kari Nordlund, daglig leder i Nordlys Elektro, setter sammen punkt 1 til 4 i markedsplanen for solcelle- og ladeavdelingen. I fjor monterte avdelingen 34 solcelleanlegg og 180 ladepunkt. Målet i år er 42 anlegg og 215 ladepunkt, og hovedmålet er 20 % vekst. Kari vil også skrive «vi skal være billigst i Oslo øst» i planen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Produktutvikling</t>
+  </si>
+  <si>
     <t xml:space="preserve">Begrepene du trenger</t>
   </si>
   <si>
+    <t xml:space="preserve">Markedsutvikling</t>
+  </si>
+  <si>
     <t xml:space="preserve">Markedsføringsform: udifferensiert (samme tilbud til alle), differensiert (eget tilbud til hver målgruppe) eller konsentrert (én gruppe). Vekststrategi: markedsinntrengning er mer av det samme i samme marked. Situasjonsanalysen: sterke og svake sider er interne (det bedriften selv rår over), muligheter og trusler er eksterne (markedet). Dekningsbidrag per enhet: det som er igjen av prisen når materiell og montørtimer er betalt. Prisdifferensiering: ulik pris til ulike kundegrupper for samme ytelse.</t>
   </si>
   <si>
+    <t xml:space="preserve">Diversifisering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sterk side</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tallene for avdelingen</t>
   </si>
   <si>
+    <t xml:space="preserve">Svak side</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prisene er uten merverdiavgift og de samme som i kapittel 3. Dekningsbidraget per enhet er det som er igjen av prisen når materiell og montørtimer er betalt (faktaarket). Omsetningen regner arket ut (grønne celler).</t>
   </si>
   <si>
+    <t xml:space="preserve">Mulighet</t>
+  </si>
+  <si>
     <t xml:space="preserve">Solcelle og lading</t>
   </si>
   <si>
@@ -96,6 +126,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ladepunkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trussel</t>
   </si>
   <si>
     <t xml:space="preserve">Antall i fjor</t>
@@ -156,27 +189,54 @@
     <t xml:space="preserve">12 montører, og Kari er installatør</t>
   </si>
   <si>
+    <t xml:space="preserve">Prisdifferensiering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostnadsbasert prissetting</t>
+  </si>
+  <si>
     <t xml:space="preserve">c) Punkt 3: målene regnet om til kroner og dekningsbidrag (hele kroner)</t>
   </si>
   <si>
+    <t xml:space="preserve">Kontantrabatt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Delmålene i kroner: 42 × 51 360 + 215 × 8 830</t>
   </si>
   <si>
     <t xml:space="preserve">kr</t>
   </si>
   <si>
+    <t xml:space="preserve">Grossist</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hovedmålet i kroner: omsetningen i fjor × 1,20</t>
   </si>
   <si>
+    <t xml:space="preserve">Detaljist</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ekstra dekningsbidrag hvis delmålene nås: bare økningen i antall × dekningsbidrag per enhet</t>
   </si>
   <si>
+    <t xml:space="preserve">Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personlig kommunikasjon</t>
+  </si>
+  <si>
     <t xml:space="preserve">d) Punkt 4: virkemidlene. Hva heter dette i boka?</t>
   </si>
   <si>
+    <t xml:space="preserve">Massekommunikasjon</t>
+  </si>
+  <si>
     <t xml:space="preserve">Borettslaget får lavere pris per ladepunkt enn eneboligen når det bestiller 20 på én gang. Hva er det?</t>
   </si>
   <si>
+    <t xml:space="preserve">Sponsing</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nordlys kjøper materiellet hos Polarlys Elektro Grossist AS. Hvilket distribusjonsledd er Polarlys?</t>
   </si>
   <si>
@@ -192,7 +252,13 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ja</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1B: Handlingsplanen for rammeavtalen: hva koster den, og bærer den seg?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nei</t>
   </si>
   <si>
     <t xml:space="preserve">Delmål 1.3 i markedsplanen er en rammeavtale med et borettslag om minst 20 ladepunkt innen 30. juni. Kari har satt opp handlingsplanen med ni linjer: hver har uke, aktivitet, timer, utlegg og ansvarlig. Budsjettkolonnen er tom. Delmålene for året gir 71 950 kr i ekstra dekningsbidrag (oppgave 1A). Styret vil kutte to av linjene for å spare penger.</t>
@@ -328,10 +394,25 @@
     <t xml:space="preserve">Karis lapp til styremøtet hadde ett mål og tre tiltak. Nå skal hele planen stå på én side, med alle sju punkter, slik at styret kan si ja. Alle tallene du trenger, står under. Skriv kort, men med tall og navn.</t>
   </si>
   <si>
+    <t xml:space="preserve">Målgruppe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Markedsplanens sju punkter i fast rekkefølge: forretningsidé og strategi, situasjonsanalyse, markedsmål, markedsstrategi (målgruppe, produkt, pris, distribusjon, påvirkning), handlingsplan, gjennomføring, evaluering. Strategien ligger fast, taktikken kan endres. Vellykket er målet nådd innenfor rammen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Pris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribusjon</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tallene du trenger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Påvirkning</t>
   </si>
   <si>
     <t xml:space="preserve">Solcelleanlegg: 34 i fjor, mål 42, 51 360 kr, 4 400 kr i dekningsbidrag. Ladepunkt: 180 i fjor, mål 215, 8 830 kr, 1 050 kr. Omsetning i fjor 3 335 640 kr. Hovedmålet er 20 % vekst innen 31. desember, ansvar Kari. Delmål 1.3 er en rammeavtale med et borettslag om minst 20 ladepunkt innen 30. juni, ansvar Kari. Handlingsplanen har 78 administrasjonstimer à 327,43 kr, 14 montørtimer à 640 kr og 5 900 kr i utlegg. Milepælen i uke 12 er at alle ti styrebesøk er gjort.</t>
@@ -364,16 +445,55 @@
     <t xml:space="preserve">Svake sider (internt)</t>
   </si>
   <si>
+    <t xml:space="preserve">Kari, daglig leder</t>
+  </si>
+  <si>
     <t xml:space="preserve">Muligheter (eksternt)</t>
   </si>
   <si>
+    <t xml:space="preserve">Styret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronny, formann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ringer to andre styrer på lista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venter til de svarer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trusler (eksternt)</t>
   </si>
   <si>
+    <t xml:space="preserve">Skriver om hele planen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justerer taktikken nå</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venter til sluttevalueringen i uke 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forkaster strategien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Målet nådd innenfor rammen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Punkt 3: markedsmålene, med tall, frist og ansvarlig</t>
   </si>
   <si>
+    <t xml:space="preserve">Målet nådd, men rammen sprakk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hovedmålet, slik det skal stå i planen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under budsjett, men målet ikke nådd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overoppfylt</t>
   </si>
   <si>
     <t xml:space="preserve">Delmål 1.3, rammeavtalen, slik det skal stå i planen</t>
@@ -751,7 +871,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -774,6 +894,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1228,7 +1352,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G52"/>
+  <dimension ref="B1:Z52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1236,446 +1360,581 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>23</v>
+      <c r="B11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="13" t="n">
         <v>180</v>
       </c>
+      <c r="Z12" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <v>215</v>
       </c>
+      <c r="Z13" s="6" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>51360</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="13" t="n">
         <v>8830</v>
       </c>
+      <c r="Z14" s="6" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>4400</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <v>1050</v>
       </c>
+      <c r="Z15" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="13" t="n">
+      <c r="B16" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="14" t="n">
         <f aca="false">C12*C14</f>
         <v>1746240</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <f aca="false">D12*D14</f>
         <v>1589400</v>
       </c>
+      <c r="Z16" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="Z17" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z18" s="0" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="Z19" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="Z20" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z21" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="Z22" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="G23" s="16" t="str">
+      <c r="B23" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="G23" s="17" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="Differensiert","Riktig. Egne tilbud til ulike målgrupper er differensiert markedsføring (10.1). Udifferensiert er samme tilbud til alle, konsentrert er én gruppe alene. Dette er ikke Porters differensiering; det er et annet valg.","Ikke riktig. Egne tilbud til ulike målgrupper er differensiert markedsføring (10.1). Udifferensiert er samme tilbud til alle, konsentrert er én gruppe alene. Dette er ikke Porters differensiering; det er et annet valg."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z23" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="G24" s="16" t="str">
+      <c r="B24" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="G24" s="17" t="str">
         <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Markedsinntrengning","Riktig. Mer av det bedriften allerede gjør, i markedet den allerede er i, er markedsinntrengning (10.1). Produktutvikling er nye produkter, markedsutvikling er nye markeder, diversifisering er begge deler.","Ikke riktig. Mer av det bedriften allerede gjør, i markedet den allerede er i, er markedsinntrengning (10.1). Produktutvikling er nye produkter, markedsutvikling er nye markeder, diversifisering er begge deler."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z24" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z25" s="0" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+      <c r="B26" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="Z26" s="6" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Svak side","Riktig. Internt: organisering og ressurser som Nordlys selv rår over (10.2). En svak side, fordi ingen eier planen.","Ikke riktig. Internt: organisering og ressurser som Nordlys selv rår over (10.2). En svak side, fordi ingen eier planen."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z27" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="G28" s="16" t="str">
+      <c r="B28" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="G28" s="17" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Svak side","Riktig. Internt: markedskommunikasjonen står på bokas liste over interne arbeidsbetingelser (10.2), selv om annonsen vises i markedet.","Ikke riktig. Internt: markedskommunikasjonen står på bokas liste over interne arbeidsbetingelser (10.2), selv om annonsen vises i markedet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z28" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="15"/>
-      <c r="G29" s="16" t="str">
+      <c r="B29" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="G29" s="17" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Mulighet","Riktig. Eksternt: markedstrender og etterspørsel (10.2). Ladepunkt er et modent volummarked.","Ikke riktig. Eksternt: markedstrender og etterspørsel (10.2). Ladepunkt er et modent volummarked."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z29" s="6" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="15"/>
-      <c r="G30" s="16" t="str">
+      <c r="B30" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="G30" s="17" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Trussel","Riktig. Eksternt: etterspørselen i markedet, som Nordlys ikke rår over (10.2).","Ikke riktig. Eksternt: etterspørselen i markedet, som Nordlys ikke rår over (10.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z30" s="6" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="15"/>
-      <c r="G31" s="16" t="str">
+      <c r="B31" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="G31" s="17" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Trussel","Riktig. Eksternt: konkurrentene, slik boka bruker dem i analysen av Bygghandel (10.2).","Ikke riktig. Eksternt: konkurrentene, slik boka bruker dem i analysen av Bygghandel (10.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z31" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="15"/>
-      <c r="G32" s="16" t="str">
+      <c r="B32" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="G32" s="17" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Sterk side","Riktig. Internt: de ansattes kompetanse (10.2). Det er dette som gjør at Nordlys kan love samme montør etterpå.","Ikke riktig. Internt: de ansattes kompetanse (10.2). Det er dette som gjør at Nordlys kan love samme montør etterpå."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z32" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z33" s="0" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
+      <c r="B34" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="Z34" s="6" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="16" t="str">
+      <c r="B35" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="17" t="str">
         <f aca="false">IF(C35="","Skriv svaret i den gule cellen.",IF(C35=(42*51360+215*8830),"Riktig.",IF(ABS(C35-(42*51360))&lt;=0,"Du har tatt bare solcelleanleggene. Legg til ladepunktene, 215 × 8 830.",IF(ABS(C35-(215*8830))&lt;=0,"Du har tatt bare ladepunktene. Legg til solcelleanleggene, 42 × 51 360.",IF(ABS(C35-(34*51360+180*8830))&lt;=0,"Det er omsetningen i fjor. Delmålene er 42 anlegg og 215 ladepunkt.",IF(ABS(C35-(3335640*1.2))&lt;=0,"Det er hovedmålet i kroner. Delmålene regnes som antall × pris for hvert produkt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z35" s="6" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G36" s="16" t="str">
+      <c r="B36" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36" s="17" t="str">
         <f aca="false">IF(C36="","Skriv svaret i den gule cellen.",IF(C36=(3335640*1.2),"Riktig.",IF(ABS(C36-(3335640*0.2))&lt;=0,"Du har regnet bare økningen, 20 %. Hovedmålet er hele omsetningen med 20 % på toppen: gang med 1,20.",IF(ABS(C36-(42*51360+215*8830))&lt;=0,"Det er delmålene i kroner. Hovedmålet er 3 335 640 × 1,20.",IF(ABS(C36-(3335640*1.02))&lt;=0,"Du har ganget med 1,02. 20 % er 1,20.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z36" s="6" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" s="17"/>
-      <c r="D37" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G37" s="16" t="str">
+      <c r="B37" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37" s="17" t="str">
         <f aca="false">IF(C37="","Skriv svaret i den gule cellen.",IF(C37=((42-34)*4400+(215-180)*1050),"Riktig.",IF(ABS(C37-(42*4400+215*1050))&lt;=0,"Du har ganget hele målet med dekningsbidraget. Det er hele årets dekningsbidrag, ikke det ekstra. Regn bare økningen: 8 anlegg og 35 ladepunkt.",IF(ABS(C37-((42-34)*4400))&lt;=0,"Du har med bare solcelleanleggene. Legg til 35 ladepunkt × 1 050.",IF(ABS(C37-((215-180)*1050))&lt;=0,"Du har med bare ladepunktene. Legg til 8 anlegg × 4 400.",IF(ABS(C37-(42*51360+215*8830-(34*51360+180*8830)))&lt;=0,"Du har regnet økningen i omsetning. Spørsmålet er dekningsbidraget: det som er igjen når materiell og montørtimer er betalt.",IF(ABS(C37-((42-34)*51360+(215-180)*8830))&lt;=0,"Du har brukt prisen, ikke dekningsbidraget per enhet.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z37" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z38" s="0" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="B39" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="Z39" s="6" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="15"/>
-      <c r="G40" s="16" t="str">
+      <c r="B40" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="16"/>
+      <c r="G40" s="17" t="str">
         <f aca="false">IF(C40="","Velg i nedtrekksmenyen.",IF(C40="Prisdifferensiering","Riktig. Ulik pris fra ulike kundegrupper for samme ytelse er prisdifferensiering (10.4.3). Kvantumsrabatt er én form for det. Kontantrabatt gjelder betalingsmåten, ikke mengden.","Ikke riktig. Ulik pris fra ulike kundegrupper for samme ytelse er prisdifferensiering (10.4.3). Kvantumsrabatt er én form for det. Kontantrabatt gjelder betalingsmåten, ikke mengden."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z40" s="6" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="15"/>
-      <c r="G41" s="16" t="str">
+      <c r="B41" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="16"/>
+      <c r="G41" s="17" t="str">
         <f aca="false">IF(C41="","Velg i nedtrekksmenyen.",IF(C41="Grossist","Riktig. Grossisten kjøper fra produsentene og selger videre til bedrifter som Nordlys (10.4.4). Detaljisten selger til forbrukere, agenten formidler uten å eie varen.","Ikke riktig. Grossisten kjøper fra produsentene og selger videre til bedrifter som Nordlys (10.4.4). Detaljisten selger til forbrukere, agenten formidler uten å eie varen."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="15"/>
-      <c r="G42" s="16" t="str">
+      <c r="B42" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="G42" s="17" t="str">
         <f aca="false">IF(C42="","Velg i nedtrekksmenyen.",IF(C42="Personlig kommunikasjon","Riktig. Ansikt til ansikt, toveis, med dybde: personlig kommunikasjon, mest brukt på bedriftsmarkedet (10.4.5). Kontaktprisen er høy, men verdien av en rammeavtale forsvarer den.","Ikke riktig. Ansikt til ansikt, toveis, med dybde: personlig kommunikasjon, mest brukt på bedriftsmarkedet (10.4.5). Kontaktprisen er høy, men verdien av en rammeavtale forsvarer den."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
+      <c r="B44" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="20" t="str">
+      <c r="B48" s="21" t="str">
         <f aca="false">IF(LEN(B45)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kostnadsleder",B45)),ISNUMBER(SEARCH("dekningsbidrag",B45))),"Bra: du sier at billigst er kostnadslederskap, og du bruker dekningsbidraget. Si gjerne også at kjedene har volumet, og at særpreget «samme montør etterpå» peker mot differensiering.",IF(OR(ISNUMBER(SEARCH("kostnadsleder",B45)),ISNUMBER(SEARCH("dekningsbidrag",B45))),"Du er på sporet. Sett navn på strategien (kostnadslederskap) og si hva prisen gjør med dekningsbidraget på 1 050 kr.","Tips: billigst er kostnadslederskap, og det krever volum og lave innkjøpspriser, som kjedene har. 5 % lavere pris på et ladepunkt er 441,50 kr, altså 42 % av dekningsbidraget på 1 050 kr. Da forsvinner pengene handlingsplanen skal betales med. Særpreget «samme montør etterpå» peker mot differensiering.")))</f>
         <v/>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C49" s="15"/>
+      <c r="B49" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="16"/>
     </row>
     <row r="50" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="22" t="str">
+      <c r="B50" s="23" t="str">
         <f aca="false">IF(C49="JA","Hint: Delmålene i kroner: 42 × 51 360 + 215 × 8 830 = 2 157 120 + 1 898 450 = 4 055 570. Hovedmålet: 3 335 640 × 1,20 = 4 002 768. Ekstra dekningsbidrag: 8 flere anlegg × 4 400 + 35 flere ladepunkt × 1 050 = 35 200 + 36 750 = 71 950. Internt er det bedriften selv rår over; eksternt er det som skjer i markedet.","")</f>
         <v/>
       </c>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
+      <c r="B52" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -1814,47 +2073,47 @@
   </conditionalFormatting>
   <dataValidations count="12">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"Udifferensiert,Differensiert,Konsentrert"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Markedsinntrengning,Produktutvikling,Markedsutvikling,Diversifisering"</formula1>
+      <formula1>$Z$4:$Z$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Sterk side,Svak side,Mulighet,Trussel"</formula1>
+      <formula1>$Z$8:$Z$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Sterk side,Svak side,Mulighet,Trussel"</formula1>
+      <formula1>$Z$12:$Z$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Sterk side,Svak side,Mulighet,Trussel"</formula1>
+      <formula1>$Z$16:$Z$19</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Sterk side,Svak side,Mulighet,Trussel"</formula1>
+      <formula1>$Z$20:$Z$23</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Sterk side,Svak side,Mulighet,Trussel"</formula1>
+      <formula1>$Z$24:$Z$27</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Sterk side,Svak side,Mulighet,Trussel"</formula1>
+      <formula1>$Z$28:$Z$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C40" type="list">
-      <formula1>"Prisdifferensiering,Kostnadsbasert prissetting,Kontantrabatt"</formula1>
+      <formula1>$Z$32:$Z$34</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C41" type="list">
-      <formula1>"Grossist,Detaljist,Agent"</formula1>
+      <formula1>$Z$35:$Z$37</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C42" type="list">
-      <formula1>"Personlig kommunikasjon,Massekommunikasjon,Sponsing"</formula1>
+      <formula1>$Z$38:$Z$40</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C49" type="list">
@@ -1877,7 +2136,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G57"/>
+  <dimension ref="B1:Z57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1885,554 +2144,595 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="Z12" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="18"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="23" t="n">
+      <c r="D14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="17"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" s="12" t="n">
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="24" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="17"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="D14" s="12" t="n">
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="17"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>1900</v>
-      </c>
-      <c r="E15" s="17"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="12" t="n">
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D20" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="17"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="23" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E17" s="17"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="17"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="17"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="17"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="24" t="n">
+      <c r="B21" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="25" t="n">
         <f aca="false">SUM(C12:C20)</f>
         <v>92</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <f aca="false">SUM(D12:D20)</f>
         <v>5900</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="14" t="n">
         <f aca="false">SUM(E12:E20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
+      <c r="B23" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="B24" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+      <c r="B26" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="25" t="str">
+        <v>97</v>
+      </c>
+      <c r="C27" s="26" t="str">
         <f aca="false">IF(E12="","Skriv svaret i cellen E12.",IF(ABS(E12-(6*327.43+0))&lt;=1,"Riktig.",IF(ABS(E12-(6*640+0))&lt;=1,"Du har brukt feil timesats. Administrasjonstimer koster 327,43 kr, montørtimer 640 kr.","Ikke riktig ennå. Budsjettpost = timer × timesats + utlegg. Sjekk at du har med både timene og utlegget.")))</f>
         <v>Skriv svaret i cellen E12.</v>
       </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="25" t="str">
+        <v>98</v>
+      </c>
+      <c r="C28" s="26" t="str">
         <f aca="false">IF(E13="","Skriv svaret i cellen E13.",IF(ABS(E13-(10*327.43+0))&lt;=1,"Riktig.",IF(ABS(E13-(10*640+0))&lt;=1,"Du har brukt feil timesats. Administrasjonstimer koster 327,43 kr, montørtimer 640 kr.","Ikke riktig ennå. Budsjettpost = timer × timesats + utlegg. Sjekk at du har med både timene og utlegget.")))</f>
         <v>Skriv svaret i cellen E13.</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
     </row>
     <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="25" t="str">
+        <v>99</v>
+      </c>
+      <c r="C29" s="26" t="str">
         <f aca="false">IF(E14="","Skriv svaret i cellen E14.",IF(ABS(E14-(14*640+0))&lt;=1,"Riktig.",IF(ABS(E14-(14*327.43+0))&lt;=1,"Du har brukt feil timesats. Administrasjonstimer koster 327,43 kr, montørtimer 640 kr.","Ikke riktig ennå. Budsjettpost = timer × timesats + utlegg. Sjekk at du har med både timene og utlegget.")))</f>
         <v>Skriv svaret i cellen E14.</v>
       </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
     </row>
     <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="25" t="str">
+        <v>100</v>
+      </c>
+      <c r="C30" s="26" t="str">
         <f aca="false">IF(E15="","Skriv svaret i cellen E15.",IF(ABS(E15-(5*327.43+1900))&lt;=1,"Riktig.",IF(ABS(E15-(5*640+1900))&lt;=1,"Du har brukt feil timesats. Administrasjonstimer koster 327,43 kr, montørtimer 640 kr.",IF(ABS(E15-(1900))&lt;=1,"Du har skrevet bare utlegget. Egne timer er ikke gratis: legg til timer × timesats.",IF(ABS(E15-(5*327.43))&lt;=1,"Du har glemt utlegget.","Ikke riktig ennå. Budsjettpost = timer × timesats + utlegg. Sjekk at du har med både timene og utlegget.")))))</f>
         <v>Skriv svaret i cellen E15.</v>
       </c>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
     </row>
     <row r="31" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="25" t="str">
+        <v>101</v>
+      </c>
+      <c r="C31" s="26" t="str">
         <f aca="false">IF(E16="","Skriv svaret i cellen E16.",IF(ABS(E16-(6*327.43+0))&lt;=1,"Riktig.",IF(ABS(E16-(6*640+0))&lt;=1,"Du har brukt feil timesats. Administrasjonstimer koster 327,43 kr, montørtimer 640 kr.","Ikke riktig ennå. Budsjettpost = timer × timesats + utlegg. Sjekk at du har med både timene og utlegget.")))</f>
         <v>Skriv svaret i cellen E16.</v>
       </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
     </row>
     <row r="32" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="25" t="str">
+        <v>102</v>
+      </c>
+      <c r="C32" s="26" t="str">
         <f aca="false">IF(E17="","Skriv svaret i cellen E17.",IF(ABS(E17-(38.5*327.43+4000))&lt;=1,"Riktig.",IF(ABS(E17-(38.5*640+4000))&lt;=1,"Du har brukt feil timesats. Administrasjonstimer koster 327,43 kr, montørtimer 640 kr.",IF(ABS(E17-(4000))&lt;=1,"Du har skrevet bare utlegget. Egne timer er ikke gratis: legg til timer × timesats.",IF(ABS(E17-(38.5*327.43))&lt;=1,"Du har glemt utlegget.","Ikke riktig ennå. Budsjettpost = timer × timesats + utlegg. Sjekk at du har med både timene og utlegget.")))))</f>
         <v>Skriv svaret i cellen E17.</v>
       </c>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
     </row>
     <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="25" t="str">
+        <v>103</v>
+      </c>
+      <c r="C33" s="26" t="str">
         <f aca="false">IF(E18="","Skriv svaret i cellen E18.",IF(ABS(E18-(4*327.43+0))&lt;=1,"Riktig.",IF(ABS(E18-(4*640+0))&lt;=1,"Du har brukt feil timesats. Administrasjonstimer koster 327,43 kr, montørtimer 640 kr.","Ikke riktig ennå. Budsjettpost = timer × timesats + utlegg. Sjekk at du har med både timene og utlegget.")))</f>
         <v>Skriv svaret i cellen E18.</v>
       </c>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="25" t="str">
+        <v>104</v>
+      </c>
+      <c r="C34" s="26" t="str">
         <f aca="false">IF(E19="","Skriv svaret i cellen E19.",IF(ABS(E19-(4*327.43+0))&lt;=1,"Riktig.",IF(ABS(E19-(4*640+0))&lt;=1,"Du har brukt feil timesats. Administrasjonstimer koster 327,43 kr, montørtimer 640 kr.","Ikke riktig ennå. Budsjettpost = timer × timesats + utlegg. Sjekk at du har med både timene og utlegget.")))</f>
         <v>Skriv svaret i cellen E19.</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
     </row>
     <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" s="25" t="str">
+        <v>105</v>
+      </c>
+      <c r="C35" s="26" t="str">
         <f aca="false">IF(E20="","Skriv svaret i cellen E20.",IF(ABS(E20-(4.5*327.43+0))&lt;=1,"Riktig.",IF(ABS(E20-(4.5*640+0))&lt;=1,"Du har brukt feil timesats. Administrasjonstimer koster 327,43 kr, montørtimer 640 kr.","Ikke riktig ennå. Budsjettpost = timer × timesats + utlegg. Sjekk at du har med både timene og utlegget.")))</f>
         <v>Skriv svaret i cellen E20.</v>
       </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
     </row>
     <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="25" t="str">
+        <v>106</v>
+      </c>
+      <c r="C36" s="26" t="str">
         <f aca="false">IF(E21="","Skriv svaret i cellen E21.",IF(ABS(E21-(78*327.43+14*640+5900))&lt;=2,"Riktig.",IF(ABS(E21-(5900))&lt;=2,"Bare utleggene er med. Egne timer er ikke gratis.",IF(ABS(E21-(78*327.43+5900))&lt;=2,"Montørtimene mangler: 14 × 640 = 8 960.","Ikke riktig ennå. Summen skal være linjene lagt sammen. Rett linjene som ikke er grønne, så stemmer summen."))))</f>
         <v>Ikke riktig ennå. Summen skal være linjene lagt sammen. Rett linjene som ikke er grønne, så stemmer summen.</v>
       </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
     </row>
     <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="26"/>
-      <c r="D38" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G38" s="16" t="str">
+      <c r="B38" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="27"/>
+      <c r="D38" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G38" s="17" t="str">
         <f aca="false">IF(C38="","Skriv svaret i den gule cellen.",IF(ABS(C38-(40400/71950*100))&lt;=0.1,"Riktig.",IF(ABS(C38-(40400/3335640*100))&lt;=0.1,"Du har delt på hele omsetningen i fjor. Del på det ekstra dekningsbidraget, 71 950 kr.",IF(ABS(C38-(40400/719930*100))&lt;=0.1,"Du har delt på økningen i omsetning. Planen skal måles mot det ekstra dekningsbidraget, 71 950 kr.",IF(ABS(C38-(71950/40400*100))&lt;=0.1,"Du har delt motsatt vei. Det er planens sum som skal deles på dekningsbidraget.",IF(ABS(C38-(40400/71950))&lt;=0.1,"Du har skrevet brøken. Gang med 100 og svar i prosent.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="16" t="str">
+      <c r="B39" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" s="17" t="str">
         <f aca="false">IF(C39="","Skriv svaret i den gule cellen.",IF(ABS(C39-(0.75*71950-40400))&lt;=2,"Riktig.",IF(ABS(C39-(71950-40400))&lt;=2,"Du har brukt hele målet. Nå nås bare 75 %: 0,75 × 71 950.",IF(ABS(C39-(0.75*71950))&lt;=2,"Du har glemt å trekke fra planens sum, 40 400.",IF(ABS(C39-(0.75*40400))&lt;=2,"Du har tatt 75 % av planen. Det er målene som nås 75 %, ikke kostnaden.",IF(ABS(C39-(40400-0.75*71950))&lt;=2,"Snu fortegnet: dekningsbidraget minus planen.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
+      <c r="B41" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" s="15"/>
-      <c r="G42" s="16" t="str">
+      <c r="B42" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="G42" s="17" t="str">
         <f aca="false">IF(C42="","Velg i nedtrekksmenyen.",IF(C42="Ja","Riktig. Uke, aktivitet, budsjett og ansvarlig: en linje i handlingsplanen (10.5, tabell 10.1).","Ikke riktig. Uke, aktivitet, budsjett og ansvarlig: en linje i handlingsplanen (10.5, tabell 10.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="15"/>
-      <c r="G43" s="16" t="str">
+      <c r="B43" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="16"/>
+      <c r="G43" s="17" t="str">
         <f aca="false">IF(C43="","Velg i nedtrekksmenyen.",IF(C43="Nei","Riktig. Målgruppevalget er punkt 4, markedsstrategien (10.4.1). Langsiktig, ikke en aktivitet i en uke.","Ikke riktig. Målgruppevalget er punkt 4, markedsstrategien (10.4.1). Langsiktig, ikke en aktivitet i en uke."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" s="15"/>
-      <c r="G44" s="16" t="str">
+      <c r="B44" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="G44" s="17" t="str">
         <f aca="false">IF(C44="","Velg i nedtrekksmenyen.",IF(C44="Nei","Riktig. Et ønske uten uke, budsjett eller navn. Ingen kan si om det ble gjort.","Ikke riktig. Et ønske uten uke, budsjett eller navn. Ingen kan si om det ble gjort."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" s="15"/>
-      <c r="G45" s="16" t="str">
+      <c r="B45" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="16"/>
+      <c r="G45" s="17" t="str">
         <f aca="false">IF(C45="","Velg i nedtrekksmenyen.",IF(C45="Ja","Riktig. En milepæl med tall, tidspunkt, budsjett og ansvarlig, slik boka vil ha det (10.7).","Ikke riktig. En milepæl med tall, tidspunkt, budsjett og ansvarlig, slik boka vil ha det (10.7)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C46" s="15"/>
-      <c r="G46" s="16" t="str">
+      <c r="B46" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="16"/>
+      <c r="G46" s="17" t="str">
         <f aca="false">IF(C46="","Velg i nedtrekksmenyen.",IF(C46="Nei","Riktig. Det overordnede målet hører til punkt 1 (10.1), og det er ikke tallfestet.","Ikke riktig. Det overordnede målet hører til punkt 1 (10.1), og det er ikke tallfestet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C47" s="15"/>
-      <c r="G47" s="16" t="str">
+      <c r="B47" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" s="16"/>
+      <c r="G47" s="17" t="str">
         <f aca="false">IF(C47="","Velg i nedtrekksmenyen.",IF(C47="Ja","Riktig. Internt tiltak med uke, mål, budsjett og ansvarlig. Intern markedsføring før ekstern.","Ikke riktig. Internt tiltak med uke, mål, budsjett og ansvarlig. Intern markedsføring før ekstern."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
+      <c r="B49" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
     </row>
     <row r="53" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="20" t="str">
+      <c r="B53" s="21" t="str">
         <f aca="false">IF(LEN(B50)&lt;40,"",IF(AND(ISNUMBER(SEARCH("intern",B50)),ISNUMBER(SEARCH("milepæl",B50))),"Bra: du har med både intern markedsføring før ekstern og milepælen som viser avvik i tide. Si gjerne også at 10 270 kr er 14 % av de 71 950 kronene som står på spill.",IF(OR(ISNUMBER(SEARCH("intern",B50)),ISNUMBER(SEARCH("milepæl",B50))),"Du har med noe av det. Oppstartsmøtet er intern markedsføring før den eksterne, og underveisevalueringen er milepælen som gjør at resultatet ikke kommer som en overraskelse.","Tips: oppstartsmøtet er intern markedsføring før ekstern; montørene som møter beboerne, må kjenne kampanjen før brevet går. Underveisevalueringen er milepælen som viser avvik mens det er tid til å justere. 10 270 kr er 14 % av de 71 950 kronene målene gir.")))</f>
         <v/>
       </c>
-      <c r="C53" s="20"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C54" s="15"/>
+      <c r="B54" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" s="16"/>
     </row>
     <row r="55" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="22" t="str">
+      <c r="B55" s="23" t="str">
         <f aca="false">IF(C54="JA","Hint: Hver linje: timer × 327,43 (montørtimer × 640) + utlegg. Brevet: 5 × 327,43 + 1 900 = 3 537. Styrebesøkene: 38,5 × 327,43 + 4 000 = 16 606. Oppstartsmøtet: 14 × 640 = 8 960. Summen er 40 400. a: 40 400 / 71 950 = 56,1 %. b: 0,75 × 71 950 − 40 400 = 13 563.","")</f>
         <v/>
       </c>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
+      <c r="B57" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -2610,27 +2910,27 @@
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C42" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C43" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C44" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C45" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C46" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C47" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$11:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C54" type="list">
@@ -2653,7 +2953,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G79"/>
+  <dimension ref="B1:Z79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2661,651 +2961,828 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z11" s="0" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="Z12" s="6" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="B13" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="Z13" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z14" s="0" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+      <c r="B15" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="Z15" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+      <c r="B16" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="Z16" s="6" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="Z17" s="6" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="Z18" s="6" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="20" t="str">
+      <c r="B19" s="21" t="str">
         <f aca="false">IF(LEN(B17)&lt;40,"",IF(AND(ISNUMBER(SEARCH("Oslo øst",B17)),ISNUMBER(SEARCH("montør",B17))),"Bra: produkt, marked (Oslo øst) og særpreget (samme montør etterpå) er med.",IF(OR(ISNUMBER(SEARCH("Oslo øst",B17)),ISNUMBER(SEARCH("montør",B17))),"Du har med noe. Forretningsidéen skal si produkt, marked og særpreg (10.1): solcelleanlegg og ladepunkt, boliger og borettslag i Oslo øst, samme montør på service etterpå.","Tips: «Nordlys leverer solcelleanlegg og ladepunkt til boliger, borettslag og sameier i Oslo øst, med samme montør på service etterpå som på montasjen.»")))</f>
         <v/>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="Z19" s="6" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="G20" s="16" t="str">
+      <c r="B20" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="G20" s="17" t="str">
         <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Markedsinntrengning","Riktig. Mer av det samme i markedet avdelingen allerede er i (10.1).","Ikke riktig. Mer av det samme i markedet avdelingen allerede er i (10.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z20" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z21" s="0" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
+      <c r="B22" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="Z22" s="6" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="B23" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="Z23" s="6" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="Z24" s="6" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="Z25" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="20" t="str">
+      <c r="B26" s="21" t="str">
         <f aca="false">IF(LEN(B24)&lt;40,"",IF(AND(ISNUMBER(SEARCH("montør",B24)),ISNUMBER(SEARCH("installatør",B24))),"Bra: 12 montører og installatøren er med.",IF(OR(ISNUMBER(SEARCH("montør",B24)),ISNUMBER(SEARCH("installatør",B24))),"Du har med noe. Interne sterke sider er det Nordlys selv rår over: 12 montører, Kari er installatør, kan love samme montør etterpå.","Tips: 12 montører, og Kari er installatør. Nordlys kan love samme montør på service etterpå.")))</f>
         <v/>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="Z26" s="6" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="B27" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="Z27" s="6" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="Z28" s="6" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="Z29" s="6" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="20" t="str">
+      <c r="B30" s="21" t="str">
         <f aca="false">IF(LEN(B28)&lt;40,"",IF(AND(ISNUMBER(SEARCH("leder",B28)),ISNUMBER(SEARCH("annonse",B28))),"Bra: ingen egen leder og aldri kjøpt annonse er med.",IF(OR(ISNUMBER(SEARCH("leder",B28)),ISNUMBER(SEARCH("annonse",B28))),"Du har med noe. De to svake sidene er at avdelingen ikke har egen leder, og at Nordlys aldri har kjøpt en annonse.","Tips: avdelingen har ingen egen leder, og Nordlys har aldri kjøpt en annonse.")))</f>
         <v/>
       </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="Z30" s="6" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="B31" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="Z31" s="6" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="Z32" s="6" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="Z33" s="6" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="20" t="str">
+      <c r="B34" s="21" t="str">
         <f aca="false">IF(LEN(B32)&lt;40,"",IF(AND(ISNUMBER(SEARCH("elbil",B32)),ISNUMBER(SEARCH("95",B32))),"Bra: elbilandelen på 95 % er med.",IF(OR(ISNUMBER(SEARCH("elbil",B32)),ISNUMBER(SEARCH("95",B32))),"Du har med noe. Muligheten er at 95 % av nye biler er elbiler: ladepunkt er et modent volummarked.","Tips: 95 % av nye biler i 2025 var elbiler (Opplysningsrådet for veitrafikken). Ladepunkt er et modent volummarked.")))</f>
         <v/>
       </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="Z34" s="6" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="B35" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="Z35" s="6" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="Z36" s="6" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="Z37" s="6" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="20" t="str">
+      <c r="B38" s="21" t="str">
         <f aca="false">IF(LEN(B36)&lt;40,"",IF(AND(ISNUMBER(SEARCH("70",B36)),ISNUMBER(SEARCH("kjede",B36))),"Bra: solmarkedet ned 70 % og kjedene er med.",IF(OR(ISNUMBER(SEARCH("70",B36)),ISNUMBER(SEARCH("kjede",B36))),"Du har med noe. Truslene er at markedet for solkraft på tak falt 70 % i 2026, og at landsdekkende kjeder selger i Oslo øst.","Tips: markedet for solkraft på tak falt rundt 70 % i 2026 (NHO Elektro). Landsdekkende kjeder selger ladepunkt i Oslo øst.")))</f>
         <v/>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="Z38" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z39" s="0" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+      <c r="B40" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="Z40" s="6" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
+      <c r="B41" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="Z41" s="6" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="Z42" s="6" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="Z43" s="6" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="20" t="str">
+      <c r="B44" s="21" t="str">
         <f aca="false">IF(LEN(B42)&lt;40,"",IF(AND(ISNUMBER(SEARCH("20 %",B42)),ISNUMBER(SEARCH("Kari",B42))),"Bra: tall, frist og ansvarlig er med.",IF(OR(ISNUMBER(SEARCH("20 %",B42)),ISNUMBER(SEARCH("Kari",B42))),"Du har med noe. Et markedsmål skal være tallfestet (20 %), knyttet til et tidspunkt (31. desember) og ha en ansvarlig (Kari) (10.3).","Tips: «Omsetningen i solcelle- og ladeavdelingen skal øke med minst 20 % mot i fjor innen 31. desember. Ansvar: Kari Nordlund.»")))</f>
         <v/>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="Z44" s="6" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
+      <c r="B45" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="Z45" s="6" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="Z46" s="6" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="Z47" s="6" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="20" t="str">
+      <c r="B48" s="21" t="str">
         <f aca="false">IF(LEN(B46)&lt;40,"",IF(AND(ISNUMBER(SEARCH("20 ladepunkt",B46)),ISNUMBER(SEARCH("juni",B46))),"Bra: antall, frist og avtalen er med.",IF(OR(ISNUMBER(SEARCH("20 ladepunkt",B46)),ISNUMBER(SEARCH("juni",B46))),"Du har med noe. Delmålet skal si minst 20 ladepunkt, innen 30. juni, og hvem som har ansvaret (Kari).","Tips: «Nordlys skal ha signert en rammeavtale med et borettslag om minst 20 ladepunkt innen 30. juni. Ansvar: Kari.»")))</f>
         <v/>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+      <c r="Z48" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z49" s="0" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
+      <c r="B50" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="Z50" s="6" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C51" s="15"/>
-      <c r="G51" s="16" t="str">
+      <c r="B51" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C51" s="16"/>
+      <c r="G51" s="17" t="str">
         <f aca="false">IF(C51="","Velg i nedtrekksmenyen.",IF(C51="Målgruppe","Riktig. Segmentering og målgruppevalg (10.4.1): segmentet har størrelse, er tilgjengelig og kan identifiseres.","Ikke riktig. Segmentering og målgruppevalg (10.4.1): segmentet har størrelse, er tilgjengelig og kan identifiseres."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z51" s="6" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="C52" s="15"/>
-      <c r="G52" s="16" t="str">
+      <c r="B52" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="16"/>
+      <c r="G52" s="17" t="str">
         <f aca="false">IF(C52="","Velg i nedtrekksmenyen.",IF(C52="Produkt","Riktig. Produktpolitikk (10.4.2): servicenivået er en del av produktet.","Ikke riktig. Produktpolitikk (10.4.2): servicenivået er en del av produktet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z52" s="6" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" s="15"/>
-      <c r="G53" s="16" t="str">
+      <c r="B53" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" s="16"/>
+      <c r="G53" s="17" t="str">
         <f aca="false">IF(C53="","Velg i nedtrekksmenyen.",IF(C53="Pris","Riktig. Prispolitikk (10.4.3): prisdifferensiering etter størrelsen på kjøpet.","Ikke riktig. Prispolitikk (10.4.3): prisdifferensiering etter størrelsen på kjøpet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z53" s="6" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C54" s="15"/>
-      <c r="G54" s="16" t="str">
+      <c r="B54" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" s="16"/>
+      <c r="G54" s="17" t="str">
         <f aca="false">IF(C54="","Velg i nedtrekksmenyen.",IF(C54="Distribusjon","Riktig. Distribusjonspolitikk (10.4.4): Nordlys er sisteleddet mot kunden, Polarlys er grossisten.","Ikke riktig. Distribusjonspolitikk (10.4.4): Nordlys er sisteleddet mot kunden, Polarlys er grossisten."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z54" s="6" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="C55" s="15"/>
-      <c r="G55" s="16" t="str">
+      <c r="B55" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" s="16"/>
+      <c r="G55" s="17" t="str">
         <f aca="false">IF(C55="","Velg i nedtrekksmenyen.",IF(C55="Påvirkning","Riktig. Markedskommunikasjon (10.4.5): brevet er massekommunikasjon, besøket er personlig kommunikasjon.","Ikke riktig. Markedskommunikasjon (10.4.5): brevet er massekommunikasjon, besøket er personlig kommunikasjon."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
+      <c r="B57" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
     </row>
     <row r="58" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="C58" s="17"/>
-      <c r="D58" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="16" t="str">
+      <c r="B58" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C58" s="18"/>
+      <c r="D58" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G58" s="17" t="str">
         <f aca="false">IF(C58="","Skriv svaret i den gule cellen.",IF(ABS(C58-(78*327.43+14*640+5900))&lt;=1,"Riktig.",IF(ABS(C58-(5900))&lt;=1,"Bare utleggene er med. Egne timer er ikke gratis.",IF(ABS(C58-(78*327.43+5900))&lt;=1,"Montørtimene mangler: 14 × 640 = 8 960.",IF(ABS(C58-(92*327.43+5900))&lt;=1,"Du har brukt 327,43 på alle timene. Montørtimene koster 640 kr.",IF(ABS(C58-(92*640+5900))&lt;=1,"Du har brukt 640 på alle timene. Administrasjonstimene koster 327,43 kr.",IF(ABS(C58-(78*327.43+14*640))&lt;=1,"Utleggene på 5 900 kr mangler.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
+      <c r="B60" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
     </row>
     <row r="61" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C61" s="15"/>
-      <c r="G61" s="16" t="str">
+      <c r="B61" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C61" s="16"/>
+      <c r="G61" s="17" t="str">
         <f aca="false">IF(C61="","Velg i nedtrekksmenyen.",IF(C61="Kari, daglig leder","Riktig. Markedssjefen har det daglige ansvaret (10.6). Uten markedssjef må rollen stå på en navngitt person: Kari. Styret og daglig leder har det øverste ansvaret.","Ikke riktig. Markedssjefen har det daglige ansvaret (10.6). Uten markedssjef må rollen stå på en navngitt person: Kari. Styret og daglig leder har det øverste ansvaret."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C62" s="15"/>
-      <c r="G62" s="16" t="str">
+      <c r="B62" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C62" s="16"/>
+      <c r="G62" s="17" t="str">
         <f aca="false">IF(C62="","Velg i nedtrekksmenyen.",IF(C62="Ringer to andre styrer på lista","Riktig. Strategien ligger fast, taktikken endres (10.6). Målet var ti besøk, ikke ti bestemte styrer. Beredskap for improvisasjon.","Ikke riktig. Strategien ligger fast, taktikken endres (10.6). Målet var ti besøk, ikke ti bestemte styrer. Beredskap for improvisasjon."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
+      <c r="B64" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B65" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C65" s="15"/>
-      <c r="G65" s="16" t="str">
+      <c r="B65" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C65" s="16"/>
+      <c r="G65" s="17" t="str">
         <f aca="false">IF(C65="","Velg i nedtrekksmenyen.",IF(C65="Justerer taktikken nå","Riktig. Milepælene skal vise om bedriften er i rute mens det er tid til å justere (10.7). Resultatet skal ikke komme som en overraskelse i juni.","Ikke riktig. Milepælene skal vise om bedriften er i rute mens det er tid til å justere (10.7). Resultatet skal ikke komme som en overraskelse i juni."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B66" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C66" s="15"/>
-      <c r="G66" s="16" t="str">
+      <c r="B66" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C66" s="16"/>
+      <c r="G66" s="17" t="str">
         <f aca="false">IF(C66="","Velg i nedtrekksmenyen.",IF(C66="Målet nådd innenfor rammen","Riktig. Avtalen kom, og planen kostet mindre enn rammen. Evaluer prosessen: hva virket?","Ikke riktig. Avtalen kom, og planen kostet mindre enn rammen. Evaluer prosessen: hva virket?"))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B67" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C67" s="15"/>
-      <c r="G67" s="16" t="str">
+      <c r="B67" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C67" s="16"/>
+      <c r="G67" s="17" t="str">
         <f aca="false">IF(C67="","Velg i nedtrekksmenyen.",IF(C67="Målet nådd, men rammen sprakk","Riktig. Avtalen kom, men 5 600 kr over rammen. Hvilke linjer ble dyrere? Ofte timene.","Ikke riktig. Avtalen kom, men 5 600 kr over rammen. Hvilke linjer ble dyrere? Ofte timene."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B68" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C68" s="15"/>
-      <c r="G68" s="16" t="str">
+      <c r="B68" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" s="16"/>
+      <c r="G68" s="17" t="str">
         <f aca="false">IF(C68="","Velg i nedtrekksmenyen.",IF(C68="Under budsjett, men målet ikke nådd","Riktig. Å bruke lite er ikke vellykket når målet glipper. Still bokas fire spørsmål (10.7).","Ikke riktig. Å bruke lite er ikke vellykket når målet glipper. Still bokas fire spørsmål (10.7)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B69" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C69" s="15"/>
-      <c r="G69" s="16" t="str">
+      <c r="B69" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C69" s="16"/>
+      <c r="G69" s="17" t="str">
         <f aca="false">IF(C69="","Velg i nedtrekksmenyen.",IF(C69="Overoppfylt","Riktig. Finn ut hvorfor det gikk bedre, og spør om ambisjonsnivået var for lavt (10.7).","Ikke riktig. Finn ut hvorfor det gikk bedre, og spør om ambisjonsnivået var for lavt (10.7)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B71" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
+      <c r="B71" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
     </row>
     <row r="72" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B72" s="19"/>
-      <c r="C72" s="19"/>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
+      <c r="B72" s="20"/>
+      <c r="C72" s="20"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
     </row>
     <row r="73" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
     </row>
     <row r="74" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="19"/>
+      <c r="B74" s="20"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
     </row>
     <row r="75" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B75" s="20" t="str">
+      <c r="B75" s="21" t="str">
         <f aca="false">IF(LEN(B72)&lt;40,"",IF(AND(ISNUMBER(SEARCH("budsjett",B72)),ISNUMBER(SEARCH("milepæl",B72))),"Bra: du har med budsjettet og milepælene. Si gjerne også at hvert tiltak nå har uke og ansvarlig, og at analysen kom før målene.",IF(OR(ISNUMBER(SEARCH("budsjett",B72)),ISNUMBER(SEARCH("milepæl",B72))),"Du har med noe. Lappen manglet analyse, frist og ansvarlig på målet, uke og navn på tiltakene, en sum styret kan si ja til, og milepæler.","Tips: lappen manglet situasjonsanalyse, frist og ansvarlig på målet, uke, navn og budsjett på hvert tiltak, en sum, og milepæler. Planen har nå alle sju punkter, 40 400 kr i budsjett og milepæler i uke 6, 7, 12, 20 og 26.")))</f>
         <v/>
       </c>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C76" s="15"/>
+      <c r="B76" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C76" s="16"/>
     </row>
     <row r="77" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B77" s="22" t="str">
+      <c r="B77" s="23" t="str">
         <f aca="false">IF(C76="JA","Hint: Forretningsidé: produkt, marked og særpreg. Analysen: internt er det Nordlys rår over, eksternt er markedet. Mål: tall, frist og navn. Handlingsplanen: 78 × 327,43 + 14 × 640 + 5 900 = 40 400. Gjennomføring: strategien ligger fast, taktikken endres. Evaluering: vellykket er målet nådd innenfor rammen.","")</f>
         <v/>
       </c>
-      <c r="C77" s="22"/>
-      <c r="D77" s="22"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="22"/>
+      <c r="C77" s="23"/>
+      <c r="D77" s="23"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="23"/>
+      <c r="G77" s="23"/>
     </row>
     <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B79" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
+      <c r="B79" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="43">
@@ -3467,55 +3944,55 @@
   </conditionalFormatting>
   <dataValidations count="14">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C20" type="list">
-      <formula1>"Markedsinntrengning,Produktutvikling,Markedsutvikling,Diversifisering"</formula1>
+      <formula1>$Z$1:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C51" type="list">
-      <formula1>"Målgruppe,Produkt,Pris,Distribusjon,Påvirkning"</formula1>
+      <formula1>$Z$5:$Z$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C52" type="list">
-      <formula1>"Målgruppe,Produkt,Pris,Distribusjon,Påvirkning"</formula1>
+      <formula1>$Z$10:$Z$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C53" type="list">
-      <formula1>"Målgruppe,Produkt,Pris,Distribusjon,Påvirkning"</formula1>
+      <formula1>$Z$15:$Z$19</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C54" type="list">
-      <formula1>"Målgruppe,Produkt,Pris,Distribusjon,Påvirkning"</formula1>
+      <formula1>$Z$20:$Z$24</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C55" type="list">
-      <formula1>"Målgruppe,Produkt,Pris,Distribusjon,Påvirkning"</formula1>
+      <formula1>$Z$25:$Z$29</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C61" type="list">
-      <formula1>"Kari,daglig leder,Styret,Ronny,formann"</formula1>
+      <formula1>$Z$30:$Z$32</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C62" type="list">
-      <formula1>"Ringer to andre styrer på lista,Venter til de svarer,Skriver om hele planen"</formula1>
+      <formula1>$Z$33:$Z$35</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C65" type="list">
-      <formula1>"Justerer taktikken nå,Venter til sluttevalueringen i uke 26,Forkaster strategien"</formula1>
+      <formula1>$Z$36:$Z$38</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C66" type="list">
-      <formula1>"Målet nådd innenfor rammen,Målet nådd,men rammen sprakk,Under budsjett,men målet ikke nådd,Overoppfylt"</formula1>
+      <formula1>$Z$39:$Z$42</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C67" type="list">
-      <formula1>"Målet nådd innenfor rammen,Målet nådd,men rammen sprakk,Under budsjett,men målet ikke nådd,Overoppfylt"</formula1>
+      <formula1>$Z$43:$Z$46</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C68" type="list">
-      <formula1>"Målet nådd innenfor rammen,Målet nådd,men rammen sprakk,Under budsjett,men målet ikke nådd,Overoppfylt"</formula1>
+      <formula1>$Z$47:$Z$50</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C69" type="list">
-      <formula1>"Målet nådd innenfor rammen,Målet nådd,men rammen sprakk,Under budsjett,men målet ikke nådd,Overoppfylt"</formula1>
+      <formula1>$Z$51:$Z$54</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C76" type="list">
@@ -3548,229 +4025,229 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="27" t="s">
-        <v>131</v>
+      <c r="B2" s="28" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>135</v>
+      <c r="B5" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="29" t="s">
-        <v>137</v>
+      <c r="B6" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="30" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="29" t="s">
-        <v>139</v>
+      <c r="B7" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="30" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="13" t="n">
+      <c r="B8" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" s="14" t="n">
         <v>4055570</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>141</v>
+      <c r="D8" s="30" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" s="13" t="n">
+      <c r="B9" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="14" t="n">
         <v>4002768</v>
       </c>
-      <c r="D9" s="29" t="s">
-        <v>143</v>
+      <c r="D9" s="30" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="13" t="n">
+      <c r="B10" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="14" t="n">
         <v>71950</v>
       </c>
-      <c r="D10" s="29" t="s">
-        <v>145</v>
+      <c r="D10" s="30" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="29" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="29" t="s">
-        <v>147</v>
+      <c r="B11" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="30" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="29" t="s">
-        <v>149</v>
+      <c r="B12" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="30" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="29" t="s">
-        <v>151</v>
+      <c r="B13" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="30" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" s="13" t="n">
+      <c r="B14" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" s="14" t="n">
         <v>40400</v>
       </c>
-      <c r="D14" s="29" t="s">
-        <v>153</v>
+      <c r="D14" s="30" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="13" t="n">
+      <c r="B15" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="14" t="n">
         <v>56.1</v>
       </c>
-      <c r="D15" s="29" t="s">
-        <v>155</v>
+      <c r="D15" s="30" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="13" t="n">
+      <c r="B16" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="14" t="n">
         <v>13563</v>
       </c>
-      <c r="D16" s="29" t="s">
-        <v>157</v>
+      <c r="D16" s="30" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="29" t="s">
-        <v>159</v>
+      <c r="B17" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="30" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="29" t="s">
-        <v>161</v>
+      <c r="B18" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="30" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="29" t="s">
-        <v>163</v>
+      <c r="B19" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="30" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="29" t="s">
-        <v>165</v>
+      <c r="B20" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="30" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="29" t="s">
-        <v>167</v>
+      <c r="B21" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="30" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="29" t="s">
-        <v>169</v>
+      <c r="B22" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="30" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="C23" s="13" t="n">
+      <c r="B23" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" s="14" t="n">
         <v>40400</v>
       </c>
-      <c r="D23" s="29" t="s">
-        <v>171</v>
+      <c r="D23" s="30" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="29" t="s">
-        <v>173</v>
+      <c r="B24" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="30" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="29" t="s">
-        <v>175</v>
+      <c r="B25" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="30" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="29" t="s">
-        <v>177</v>
+      <c r="B26" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="30" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ma10/MA10_Markedsplanen_oppsummert_Oppgaver_v6.xlsx
+++ b/pensum/ma10/MA10_Markedsplanen_oppsummert_Oppgaver_v6.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">1A  Punkt 1–4 i markedsplanen for solcelle og lading: henger de sammen?</t>
   </si>
   <si>
-    <t xml:space="preserve">1B  Handlingsplanen for rammeavtalen: hva koster den, og bærer den seg?</t>
+    <t xml:space="preserve">1B  Handlingsplanen for ladeanlegget: hva koster den, og bærer den seg?</t>
   </si>
   <si>
     <t xml:space="preserve">1C  Hele markedsplanen for solcelle og lading på én side</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Markedsinntrengning</t>
   </si>
   <si>
-    <t xml:space="preserve">Kari Nordlund, daglig leder i Nordlys Elektro, setter sammen punkt 1 til 4 i markedsplanen for solcelle- og ladeavdelingen. I fjor monterte avdelingen 34 solcelleanlegg og 180 ladepunkt. Målet i år er 42 anlegg og 215 ladepunkt, og hovedmålet er 20 % vekst. Kari vil også skrive «vi skal være billigst i Oslo øst» i planen.</t>
+    <t xml:space="preserve">Kari Nordlund, daglig leder i Nordlys Elektro, setter sammen punkt 1 til 4 i markedsplanen for solcelle- og ladeavdelingen. I fjor monterte avdelingen 34 solcelleanlegg og 180 ladepunkt. Målet i år er Idas nye miks fra kapittel 3, 30 anlegg og 282 ladepunkt, og hovedmålet er 20 % vekst. Kari vil også skrive «vi skal være billigst i Oslo øst» i planen.</t>
   </si>
   <si>
     <t xml:space="preserve">Produktutvikling</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">Markedsutvikling</t>
   </si>
   <si>
-    <t xml:space="preserve">Markedsføringsform: udifferensiert (samme tilbud til alle), differensiert (eget tilbud til hver målgruppe) eller konsentrert (én gruppe). Vekststrategi: markedsinntrengning er mer av det samme i samme marked. Situasjonsanalysen: sterke og svake sider er interne (det bedriften selv rår over), muligheter og trusler er eksterne (markedet). Dekningsbidrag per enhet: det som er igjen av prisen når materiell og montørtimer er betalt. Prisdifferensiering: ulik pris til ulike kundegrupper for samme ytelse.</t>
+    <t xml:space="preserve">Markedsføringsform: udifferensiert (samme tilbud til alle), differensiert (eget tilbud til hver målgruppe) eller konsentrert (én gruppe). Vekststrategi: markedsinntrengning er mer av det samme til de samme kundene, markedsutvikling er samme produkt til en ny kundegruppe. Situasjonsanalysen: sterke og svake sider er interne (det bedriften selv rår over), muligheter og trusler er eksterne (markedet). Dekningsbidrag per enhet: det som er igjen av prisen når materiell og montørtimer er betalt. Prisdifferensiering: ulik pris til ulike kundegrupper for samme ytelse.</t>
   </si>
   <si>
     <t xml:space="preserve">Diversifisering</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">Svak side</t>
   </si>
   <si>
-    <t xml:space="preserve">Prisene er uten merverdiavgift og de samme som i kapittel 3. Dekningsbidraget per enhet er det som er igjen av prisen når materiell og montørtimer er betalt (faktaarket). Omsetningen regner arket ut (grønne celler).</t>
+    <t xml:space="preserve">Prisene er uten merverdiavgift og de samme som i kapittel 3. Målene er Idas nye miks fra kapittel 3: færre solcelleanlegg, fordi solkraft på tak falt om lag 70 % i første del av 2026 (NHO Elektro, april 2026), og flere ladepunkt. Dekningsbidraget per enhet er det som er igjen av prisen når materiell og montørtimer er betalt (faktaarket). Omsetningen regner arket ut (grønne celler).</t>
   </si>
   <si>
     <t xml:space="preserve">Mulighet</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">Omsetning i fjor, kr (antall × pris)</t>
   </si>
   <si>
-    <t xml:space="preserve">Omsetningen i fjor til sammen: 1 746 240 + 1 589 400 = 3 335 640 kr. Hovedmålet er 20 % vekst i år.</t>
+    <t xml:space="preserve">Omsetningen i fjor til sammen: 1 974 040 + 1 724 400 = 3 698 440 kr. Hovedmålet er 20 % vekst i år.</t>
   </si>
   <si>
     <t xml:space="preserve">Oppgaven, trinn for trinn</t>
@@ -165,7 +165,7 @@
     <t xml:space="preserve">Eneboligkunden får fastpris gjennom en annonse. Borettslagsstyret får befaring, kvantumsrabatt og besøk. Hvilken markedsføringsform er det?</t>
   </si>
   <si>
-    <t xml:space="preserve">Avdelingen skal vokse ved å selge mer av det samme til boliger og borettslag i Oslo øst. Hvilken vekststrategi er det?</t>
+    <t xml:space="preserve">Avdelingen har solgt mest til eneboliger. Nå skal veksten komme fra en ny kundegruppe, borettslagene, med de samme anleggene. Hvilken vekststrategi er det?</t>
   </si>
   <si>
     <t xml:space="preserve">b) Punkt 2: situasjonsanalysen. Rår Nordlys over dette selv (internt), eller skjer det i markedet (eksternt)?</t>
@@ -177,10 +177,10 @@
     <t xml:space="preserve">Nordlys har aldri kjøpt en annonse</t>
   </si>
   <si>
-    <t xml:space="preserve">95 % av nye biler i Norge var elbiler i 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Markedet for solkraft på tak falt rundt 70 % i 2026</t>
+    <t xml:space="preserve">Over 90 % av nye biler i Norge var elbiler i 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solkraft på tak falt om lag 70 % i første del av 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Landsdekkende kjeder selger ladepunkt i Oslo øst</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Kontantrabatt</t>
   </si>
   <si>
-    <t xml:space="preserve">Delmålene i kroner: 42 × 51 360 + 215 × 8 830</t>
+    <t xml:space="preserve">Delmålene i kroner: 30 × 58 060 + 282 × 9 580</t>
   </si>
   <si>
     <t xml:space="preserve">kr</t>
@@ -216,7 +216,7 @@
     <t xml:space="preserve">Detaljist</t>
   </si>
   <si>
-    <t xml:space="preserve">Ekstra dekningsbidrag hvis delmålene nås: bare økningen i antall × dekningsbidrag per enhet</t>
+    <t xml:space="preserve">Ekstra dekningsbidrag hvis delmålene nås: bare endringen i antall × dekningsbidrag per enhet (anleggene går ned)</t>
   </si>
   <si>
     <t xml:space="preserve">Agent</t>
@@ -243,7 +243,7 @@
     <t xml:space="preserve">Kari og Tom besøker borettslagsstyret og går gjennom tilbudet. Hvilken kommunikasjonsform er det?</t>
   </si>
   <si>
-    <t xml:space="preserve">e) Kari vil skrive «vi skal være billigst i Oslo øst» som konkurransestrategi i punkt 1. Henger det sammen med situasjonsanalysen og målene? Bruk tallene: 5 % lavere pris på et ladepunkt er 441,50 kr av 1 050 kr i dekningsbidrag. To setninger.</t>
+    <t xml:space="preserve">e) Kari vil skrive «vi skal være billigst i Oslo øst» som konkurransestrategi i punkt 1. Henger det sammen med situasjonsanalysen og målene? Bruk tallene: 5 % lavere pris på et ladepunkt er 479 kr av 1 800 kr i dekningsbidrag. To setninger.</t>
   </si>
   <si>
     <t xml:space="preserve">Står du fast? Skriv JA i den gule cellen:</t>
@@ -255,16 +255,16 @@
     <t xml:space="preserve">Ja</t>
   </si>
   <si>
-    <t xml:space="preserve">Oppgave 1B: Handlingsplanen for rammeavtalen: hva koster den, og bærer den seg?</t>
+    <t xml:space="preserve">Oppgave 1B: Handlingsplanen for ladeanlegget: hva koster den, og bærer den seg?</t>
   </si>
   <si>
     <t xml:space="preserve">Nei</t>
   </si>
   <si>
-    <t xml:space="preserve">Delmål 1.3 i markedsplanen er en rammeavtale med et borettslag om minst 20 ladepunkt innen 30. juni. Kari har satt opp handlingsplanen med ni linjer: hver har uke, aktivitet, timer, utlegg og ansvarlig. Budsjettkolonnen er tom. Delmålene for året gir 71 950 kr i ekstra dekningsbidrag (oppgave 1A). Styret vil kutte to av linjene for å spare penger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Handlingsplan (aktivitetsplan): den kortsiktige iverksettelsen av strategien, med uke, aktivitet, mål, budsjett og ansvarlig (tabell 10.1). Budsjettpost = timer × timesats + utlegg. Egne timer er ikke gratis selv om lønna løper. Milepæl: et delmål med dato underveis, så avvik oppdages i tide.</t>
+    <t xml:space="preserve">Delmål 1.3 i markedsplanen er en signert kontrakt med et borettslag om et felles ladeanlegg med minst 20 plasser innen 30. juni. Kari har satt opp handlingsplanen med ni linjer: hver har uke, aktivitet, timer, utlegg og ansvarlig. Budsjettkolonnen er tom. Delmålene for året gir 139 200 kr i ekstra dekningsbidrag (oppgave 1A). Styret vil kutte to av linjene for å spare penger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handlingsplan (aktivitetsplan): den kortsiktige iverksettelsen av strategien, med uke, aktivitet, mål, budsjett og ansvarlig (tabell 10.1). Budsjettpost = timer × timesats + utlegg. Egne timer står i budsjettet med lønnskostnaden. Med ledig kapasitet koster de ingenting ekstra; med full kalender koster en montørtime 890 kr i tapt fakturering. Milepæl: et delmål med dato underveis, så avvik oppdages i tide.</t>
   </si>
   <si>
     <t xml:space="preserve">Timesatsene</t>
@@ -317,7 +317,7 @@
   <si>
     <t xml:space="preserve">1. Regn budsjettet for hver linje: timer × timesats + utlegg, i hele kroner. Arket summerer nederst.
 2. Sjekk linjene under. «Riktig» betyr at tallet stemmer.
-3. Svar på a og b: hvor stor del av det ekstra dekningsbidraget på 71 950 kr (fra 1A) planen bruker, og hva som er igjen hvis tre firedeler av målene nås.
+3. Svar på a og b: hvor stor del av det ekstra dekningsbidraget på 139 200 kr (fra 1A) planen bruker, og hva som er igjen hvis tre firedeler av målene nås.
 4. Velg for seks utsagn om de hører hjemme i en handlingsplan.
 5. Svar styret i d.</t>
   </si>
@@ -355,13 +355,13 @@
     <t xml:space="preserve">Summen av planen:</t>
   </si>
   <si>
-    <t xml:space="preserve">a) Hvor stor del av det ekstra dekningsbidraget (71 950 kr) bruker planen? I prosent med én desimal (skriv 56,1 for 56,1 %)</t>
+    <t xml:space="preserve">a) Hvor stor del av det ekstra dekningsbidraget (139 200 kr) bruker planen? I prosent med én desimal (skriv 29,0 for 29,0 %)</t>
   </si>
   <si>
     <t xml:space="preserve">%</t>
   </si>
   <si>
-    <t xml:space="preserve">b) Hva er igjen hvis 75 % av målene nås? 0,75 × 71 950 − planens sum, i hele kroner</t>
+    <t xml:space="preserve">b) Hva er igjen hvis 75 % av målene nås? 0,75 × 139 200 − planens sum, i hele kroner</t>
   </si>
   <si>
     <t xml:space="preserve">c) Hører dette hjemme i handlingsplanen (uke, aktivitet, mål, budsjett og ansvarlig)?</t>
@@ -415,7 +415,7 @@
     <t xml:space="preserve">Påvirkning</t>
   </si>
   <si>
-    <t xml:space="preserve">Solcelleanlegg: 34 i fjor, mål 42, 51 360 kr, 4 400 kr i dekningsbidrag. Ladepunkt: 180 i fjor, mål 215, 8 830 kr, 1 050 kr. Omsetning i fjor 3 335 640 kr. Hovedmålet er 20 % vekst innen 31. desember, ansvar Kari. Delmål 1.3 er en rammeavtale med et borettslag om minst 20 ladepunkt innen 30. juni, ansvar Kari. Handlingsplanen har 78 administrasjonstimer à 327,43 kr, 14 montørtimer à 640 kr og 5 900 kr i utlegg. Milepælen i uke 12 er at alle ti styrebesøk er gjort.</t>
+    <t xml:space="preserve">Solcelleanlegg: 34 i fjor, mål 30, 58 060 kr, 11 100 kr i dekningsbidrag. Ladepunkt: 180 i fjor, mål 282, 9 580 kr, 1 800 kr. Omsetning i fjor 3 698 440 kr. Hovedmålet er 20 % vekst innen 31. desember, ansvar Kari. Delmål 1.3 er en signert kontrakt med et borettslag om et felles ladeanlegg med minst 20 plasser innen 30. juni, ansvar Kari. Handlingsplanen har 78 administrasjonstimer à 327,43 kr, 14 montørtimer à 640 kr og 5 900 kr i utlegg. Milepælen i uke 12 er at alle ti styrebesøk er gjort.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Skriv forretningsidéen (produkt, marked og særpreg) og velg vekststrategi.
@@ -496,7 +496,7 @@
     <t xml:space="preserve">Overoppfylt</t>
   </si>
   <si>
-    <t xml:space="preserve">Delmål 1.3, rammeavtalen, slik det skal stå i planen</t>
+    <t xml:space="preserve">Delmål 1.3, kontrakten om et felles ladeanlegg, slik det skal stå i planen</t>
   </si>
   <si>
     <t xml:space="preserve">Punkt 4: markedsstrategien. Hvilket ledd hører tiltaket til?</t>
@@ -508,7 +508,7 @@
     <t xml:space="preserve">Samme montør på service etterpå som på montasjen</t>
   </si>
   <si>
-    <t xml:space="preserve">Kvantumsrabatt til borettslag som bestiller 20 ladepunkt</t>
+    <t xml:space="preserve">Kvantumsrabatt til borettslag som bestiller et felles ladeanlegg med 20 plasser</t>
   </si>
   <si>
     <t xml:space="preserve">Materiellet hentes hos Polarlys dagen før montasje</t>
@@ -538,16 +538,16 @@
     <t xml:space="preserve">Uke 12: bare 4 av 10 styrebesøk er gjort. Hva gjør Kari?</t>
   </si>
   <si>
-    <t xml:space="preserve">A: én avtale i uke 20, kostet 38 000 kr (ramme 40 400)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B: én avtale, men kostet 46 000 kr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C: ingen avtale, kostet 31 000 kr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D: tre avtaler, kostet 40 000 kr</t>
+    <t xml:space="preserve">A: én kontrakt i uke 20, kostet 38 000 kr (ramme 40 400)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B: én kontrakt, men kostet 46 000 kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C: ingen kontrakt, kostet 31 000 kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D: tre kontrakter, kostet 40 000 kr</t>
   </si>
   <si>
     <t xml:space="preserve">Til slutt: Karis lapp hadde ett mål og tre tiltak. Hva manglet, og hva har planen nå? To–tre setninger.</t>
@@ -571,31 +571,31 @@
     <t xml:space="preserve">1A a) Strategien</t>
   </si>
   <si>
-    <t xml:space="preserve">Differensiert markedsføring (egne tilbud til eneboligen og styret). Vekst ved markedsinntrengning (mer av det samme i Oslo øst)</t>
+    <t xml:space="preserve">Differensiert markedsføring (egne tilbud til eneboligen og styret). Vekst ved markedsutvikling (samme anlegg til en ny kundegruppe, borettslagene)</t>
   </si>
   <si>
     <t xml:space="preserve">1A b) Analysen</t>
   </si>
   <si>
-    <t xml:space="preserve">Svake sider: ingen egen leder, aldri kjøpt annonse. Sterk side: 12 montører og installatør. Mulighet: 95 % elbiler. Trusler: solkraft ned 70 %, kjedene i Oslo øst</t>
+    <t xml:space="preserve">Svake sider: ingen egen leder, aldri kjøpt annonse. Sterk side: 12 montører og installatør. Mulighet: over 90 % elbiler. Trusler: solkraft ned om lag 70 % i første del av 2026, kjedene i Oslo øst</t>
   </si>
   <si>
     <t xml:space="preserve">1A c) Delmålene i kroner</t>
   </si>
   <si>
-    <t xml:space="preserve">42 × 51 360 + 215 × 8 830 = 2 157 120 + 1 898 450 = 4 055 570 kr</t>
+    <t xml:space="preserve">30 × 58 060 + 282 × 9 580 = 1 741 800 + 2 701 560 = 4 443 360 kr</t>
   </si>
   <si>
     <t xml:space="preserve">1A c) Hovedmålet i kroner</t>
   </si>
   <si>
-    <t xml:space="preserve">3 335 640 × 1,20 = 4 002 768 kr. Delmålene bærer hovedmålet med 52 802 kr i margin</t>
+    <t xml:space="preserve">3 698 440 × 1,20 = 4 438 128 kr. Delmålene bærer hovedmålet med 5 232 kr i margin; med ett ladepunkt færre ryker det</t>
   </si>
   <si>
     <t xml:space="preserve">1A c) Ekstra dekningsbidrag</t>
   </si>
   <si>
-    <t xml:space="preserve">8 × 4 400 + 35 × 1 050 = 35 200 + 36 750 = 71 950 kr. Bare økningen, ikke hele året (410 550)</t>
+    <t xml:space="preserve">102 × 1 800 − 4 × 11 100 = 183 600 − 44 400 = 139 200 kr. Bare endringen, ikke hele året (840 600), og anleggene som faller bort, trekkes fra</t>
   </si>
   <si>
     <t xml:space="preserve">1A d) Virkemidlene</t>
@@ -607,7 +607,7 @@
     <t xml:space="preserve">1A e) Til Kari</t>
   </si>
   <si>
-    <t xml:space="preserve">Billigst er kostnadslederskap, og kjedene har volumet og innkjøpsprisene. 5 % lavere pris på et ladepunkt er 441,50 kr, 42 % av dekningsbidraget på 1 050 kr; da forsvinner pengene handlingsplanen skal betales med. Særpreget «samme montør etterpå» peker mot differensiering</t>
+    <t xml:space="preserve">Billigst er kostnadslederskap, og kjedene har volumet og innkjøpsprisene. 5 % lavere pris på et ladepunkt er 479 kr, 26,6 % av dekningsbidraget på 1 800 kr; da forsvinner pengene handlingsplanen skal betales med. Særpreget «samme montør etterpå» peker mot differensiering</t>
   </si>
   <si>
     <t xml:space="preserve">1B Budsjettlinjene</t>
@@ -625,13 +625,13 @@
     <t xml:space="preserve">1B a) Andel av ekstra dekningsbidrag</t>
   </si>
   <si>
-    <t xml:space="preserve">40 400 / 71 950 = 56,1 % (56,2 med avrundet sum; begge godtas). Når under 56 % av målene, bærer planen seg ikke i år</t>
+    <t xml:space="preserve">40 400 / 139 200 = 29,0 %. Nås under 29 % av målene, bærer planen seg ikke i år</t>
   </si>
   <si>
     <t xml:space="preserve">1B b) Igjen ved 75 %</t>
   </si>
   <si>
-    <t xml:space="preserve">0,75 × 71 950 − 40 400 = 53 963 − 40 400 = 13 563 kr</t>
+    <t xml:space="preserve">0,75 × 139 200 − 40 400 = 104 400 − 40 400 = 64 000 kr</t>
   </si>
   <si>
     <t xml:space="preserve">1B c) Hører hjemme</t>
@@ -643,25 +643,25 @@
     <t xml:space="preserve">1B d) Til styret</t>
   </si>
   <si>
-    <t xml:space="preserve">Oppstartsmøtet er intern markedsføring før ekstern. Underveisevalueringen er milepælen som viser avvik mens det er tid. Gjennomføringen må få nok ressurser (10.6). 10 270 kr er 14 % av de 71 950 kr som står på spill</t>
+    <t xml:space="preserve">Oppstartsmøtet er intern markedsføring før ekstern. Underveisevalueringen er milepælen som viser avvik mens det er tid. Gjennomføringen må få nok ressurser (10.6). 10 270 kr er 7,4 % av de 139 200 kr som står på spill</t>
   </si>
   <si>
     <t xml:space="preserve">1C Punkt 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Solcelleanlegg og ladepunkt til boliger, borettslag og sameier i Oslo øst, med samme montør på service etterpå. Markedsinntrengning</t>
+    <t xml:space="preserve">Solcelleanlegg og ladepunkt til boliger, borettslag og sameier i Oslo øst, med samme montør på service etterpå. Markedsutvikling mot borettslagene</t>
   </si>
   <si>
     <t xml:space="preserve">1C Punkt 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Sterk: 12 montører, Kari er installatør. Svak: ingen egen leder, aldri kjøpt annonse. Mulighet: 95 % elbiler. Trussel: solkraft ned 70 %, kjedene</t>
+    <t xml:space="preserve">Sterk: 12 montører, Kari er installatør. Svak: ingen egen leder, aldri kjøpt annonse. Mulighet: over 90 % elbiler. Trussel: solkraft ned om lag 70 % i første del av 2026, kjedene</t>
   </si>
   <si>
     <t xml:space="preserve">1C Punkt 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Hovedmål: minst 20 % vekst innen 31. desember, ansvar Kari. Delmål 1.3: rammeavtale om minst 20 ladepunkt innen 30. juni, ansvar Kari</t>
+    <t xml:space="preserve">Hovedmål: minst 20 % vekst innen 31. desember, ansvar Kari. Delmål 1.3: kontrakt om et felles ladeanlegg med minst 20 plasser innen 30. juni, ansvar Kari</t>
   </si>
   <si>
     <t xml:space="preserve">1C Punkt 4</t>
@@ -1464,7 +1464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
         <v>29</v>
       </c>
@@ -1510,10 +1510,10 @@
         <v>36</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>215</v>
+        <v>282</v>
       </c>
       <c r="Z13" s="6" t="s">
         <v>28</v>
@@ -1524,10 +1524,10 @@
         <v>37</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>51360</v>
+        <v>58060</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>8830</v>
+        <v>9580</v>
       </c>
       <c r="Z14" s="6" t="s">
         <v>30</v>
@@ -1538,10 +1538,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>4400</v>
+        <v>11100</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="Z15" s="6" t="s">
         <v>34</v>
@@ -1553,11 +1553,11 @@
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">C12*C14</f>
-        <v>1746240</v>
+        <v>1974040</v>
       </c>
       <c r="D16" s="14" t="n">
         <f aca="false">D12*D14</f>
-        <v>1589400</v>
+        <v>1724400</v>
       </c>
       <c r="Z16" s="6" t="s">
         <v>26</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C24" s="16"/>
       <c r="G24" s="17" t="str">
-        <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Markedsinntrengning","Riktig. Mer av det bedriften allerede gjør, i markedet den allerede er i, er markedsinntrengning (10.1). Produktutvikling er nye produkter, markedsutvikling er nye markeder, diversifisering er begge deler.","Ikke riktig. Mer av det bedriften allerede gjør, i markedet den allerede er i, er markedsinntrengning (10.1). Produktutvikling er nye produkter, markedsutvikling er nye markeder, diversifisering er begge deler."))</f>
+        <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Markedsutvikling","Riktig. Samme produkt til en ny kundegruppe er markedsutvikling (10.1). Markedsinntrengning er mer av det samme til de kundene en allerede har, produktutvikling er nye produkter, diversifisering er begge deler.","Ikke riktig. Samme produkt til en ny kundegruppe er markedsutvikling (10.1). Markedsinntrengning er mer av det samme til de kundene en allerede har, produktutvikling er nye produkter, diversifisering er begge deler."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z24" s="6" t="s">
@@ -1774,7 +1774,7 @@
         <v>58</v>
       </c>
       <c r="G35" s="17" t="str">
-        <f aca="false">IF(C35="","Skriv svaret i den gule cellen.",IF(C35=(42*51360+215*8830),"Riktig.",IF(ABS(C35-(42*51360))&lt;=0,"Du har tatt bare solcelleanleggene. Legg til ladepunktene, 215 × 8 830.",IF(ABS(C35-(215*8830))&lt;=0,"Du har tatt bare ladepunktene. Legg til solcelleanleggene, 42 × 51 360.",IF(ABS(C35-(34*51360+180*8830))&lt;=0,"Det er omsetningen i fjor. Delmålene er 42 anlegg og 215 ladepunkt.",IF(ABS(C35-(3335640*1.2))&lt;=0,"Det er hovedmålet i kroner. Delmålene regnes som antall × pris for hvert produkt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
+        <f aca="false">IF(C35="","Skriv svaret i den gule cellen.",IF(C35=(30*58060+282*9580),"Riktig.",IF(ABS(C35-(30*58060))&lt;=0,"Du har tatt bare solcelleanleggene. Legg til ladepunktene, 282 × 9 580.",IF(ABS(C35-(282*9580))&lt;=0,"Du har tatt bare ladepunktene. Legg til solcelleanleggene, 30 × 58 060.",IF(ABS(C35-(34*58060+180*9580))&lt;=0,"Det er omsetningen i fjor. Delmålene er 30 anlegg og 282 ladepunkt.",IF(ABS(C35-(42*58060+215*9580))&lt;=0,"Det er den første miksen fra kapittel 3, med 42 anlegg. Den ble forkastet fordi solmarkedet falt. Bruk Idas nye miks: 30 anlegg og 282 ladepunkt.",IF(ABS(C35-(3698440*1.2))&lt;=0,"Det er hovedmålet i kroner. Delmålene regnes som antall × pris for hvert produkt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
       <c r="Z35" s="6" t="s">
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="G36" s="17" t="str">
-        <f aca="false">IF(C36="","Skriv svaret i den gule cellen.",IF(C36=(3335640*1.2),"Riktig.",IF(ABS(C36-(3335640*0.2))&lt;=0,"Du har regnet bare økningen, 20 %. Hovedmålet er hele omsetningen med 20 % på toppen: gang med 1,20.",IF(ABS(C36-(42*51360+215*8830))&lt;=0,"Det er delmålene i kroner. Hovedmålet er 3 335 640 × 1,20.",IF(ABS(C36-(3335640*1.02))&lt;=0,"Du har ganget med 1,02. 20 % er 1,20.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
+        <f aca="false">IF(C36="","Skriv svaret i den gule cellen.",IF(C36=(3698440*1.2),"Riktig.",IF(ABS(C36-(3698440*0.2))&lt;=0,"Du har regnet bare økningen, 20 %. Hovedmålet er hele omsetningen med 20 % på toppen: gang med 1,20.",IF(ABS(C36-(30*58060+282*9580))&lt;=0,"Det er delmålene i kroner. Hovedmålet er 3 698 440 × 1,20.",IF(ABS(C36-(3698440*1.02))&lt;=0,"Du har ganget med 1,02. 20 % er 1,20.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
       <c r="Z36" s="6" t="s">
@@ -1806,7 +1806,7 @@
         <v>58</v>
       </c>
       <c r="G37" s="17" t="str">
-        <f aca="false">IF(C37="","Skriv svaret i den gule cellen.",IF(C37=((42-34)*4400+(215-180)*1050),"Riktig.",IF(ABS(C37-(42*4400+215*1050))&lt;=0,"Du har ganget hele målet med dekningsbidraget. Det er hele årets dekningsbidrag, ikke det ekstra. Regn bare økningen: 8 anlegg og 35 ladepunkt.",IF(ABS(C37-((42-34)*4400))&lt;=0,"Du har med bare solcelleanleggene. Legg til 35 ladepunkt × 1 050.",IF(ABS(C37-((215-180)*1050))&lt;=0,"Du har med bare ladepunktene. Legg til 8 anlegg × 4 400.",IF(ABS(C37-(42*51360+215*8830-(34*51360+180*8830)))&lt;=0,"Du har regnet økningen i omsetning. Spørsmålet er dekningsbidraget: det som er igjen når materiell og montørtimer er betalt.",IF(ABS(C37-((42-34)*51360+(215-180)*8830))&lt;=0,"Du har brukt prisen, ikke dekningsbidraget per enhet.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))))</f>
+        <f aca="false">IF(C37="","Skriv svaret i den gule cellen.",IF(C37=((30-34)*11100+(282-180)*1800),"Riktig.",IF(ABS(C37-(30*11100+282*1800))&lt;=0,"Du har ganget hele målet med dekningsbidraget. Det er hele årets dekningsbidrag, ikke det ekstra. Regn bare endringen: 4 færre anlegg og 102 flere ladepunkt.",IF(ABS(C37-((282-180)*1800))&lt;=0,"Du har med bare ladepunktene. Fire færre anlegg trekker fra: −4 × 11 100 = −44 400.",IF(ABS(C37-((34-30)*11100+(282-180)*1800))&lt;=0,"Du har lagt til solcelleanleggene, men de går ned fra 34 til 30. De fire anleggene som faller bort, trekker 44 400 fra.",IF(ABS(C37-((30-34)*11100))&lt;=0,"Du har med bare solcelleanleggene. Legg til 102 ladepunkt × 1 800.",IF(ABS(C37-(30*58060+282*9580-(34*58060+180*9580)))&lt;=0,"Du har regnet økningen i omsetning (eller brukt prisen i stedet for dekningsbidraget). Spørsmålet er dekningsbidraget: det som er igjen når materiell og montørtimer er betalt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
       <c r="Z37" s="6" t="s">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C42" s="16"/>
       <c r="G42" s="17" t="str">
-        <f aca="false">IF(C42="","Velg i nedtrekksmenyen.",IF(C42="Personlig kommunikasjon","Riktig. Ansikt til ansikt, toveis, med dybde: personlig kommunikasjon, mest brukt på bedriftsmarkedet (10.4.5). Kontaktprisen er høy, men verdien av en rammeavtale forsvarer den.","Ikke riktig. Ansikt til ansikt, toveis, med dybde: personlig kommunikasjon, mest brukt på bedriftsmarkedet (10.4.5). Kontaktprisen er høy, men verdien av en rammeavtale forsvarer den."))</f>
+        <f aca="false">IF(C42="","Velg i nedtrekksmenyen.",IF(C42="Personlig kommunikasjon","Riktig. Ansikt til ansikt, toveis, med dybde: personlig kommunikasjon, mest brukt på bedriftsmarkedet (10.4.5). Kontaktprisen er høy, men verdien av en kontrakt om et felles ladeanlegg, 82 500 kr i dekningsbidrag, forsvarer den.","Ikke riktig. Ansikt til ansikt, toveis, med dybde: personlig kommunikasjon, mest brukt på bedriftsmarkedet (10.4.5). Kontaktprisen er høy, men verdien av en kontrakt om et felles ladeanlegg, 82 500 kr i dekningsbidrag, forsvarer den."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="21" t="str">
-        <f aca="false">IF(LEN(B45)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kostnadsleder",B45)),ISNUMBER(SEARCH("dekningsbidrag",B45))),"Bra: du sier at billigst er kostnadslederskap, og du bruker dekningsbidraget. Si gjerne også at kjedene har volumet, og at særpreget «samme montør etterpå» peker mot differensiering.",IF(OR(ISNUMBER(SEARCH("kostnadsleder",B45)),ISNUMBER(SEARCH("dekningsbidrag",B45))),"Du er på sporet. Sett navn på strategien (kostnadslederskap) og si hva prisen gjør med dekningsbidraget på 1 050 kr.","Tips: billigst er kostnadslederskap, og det krever volum og lave innkjøpspriser, som kjedene har. 5 % lavere pris på et ladepunkt er 441,50 kr, altså 42 % av dekningsbidraget på 1 050 kr. Da forsvinner pengene handlingsplanen skal betales med. Særpreget «samme montør etterpå» peker mot differensiering.")))</f>
+        <f aca="false">IF(LEN(B45)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kostnadsleder",B45)),ISNUMBER(SEARCH("dekningsbidrag",B45))),"Bra: du sier at billigst er kostnadslederskap, og du bruker dekningsbidraget. Si gjerne også at kjedene har volumet, og at særpreget «samme montør etterpå» peker mot differensiering.",IF(OR(ISNUMBER(SEARCH("kostnadsleder",B45)),ISNUMBER(SEARCH("dekningsbidrag",B45))),"Du er på sporet. Sett navn på strategien (kostnadslederskap) og si hva prisen gjør med dekningsbidraget på 1 800 kr.","Tips: billigst er kostnadslederskap, og det krever volum og lave innkjøpspriser, som kjedene har. 5 % lavere pris på et ladepunkt er 479 kr, altså 26,6 % av dekningsbidraget på 1 800 kr. Da forsvinner pengene handlingsplanen skal betales med. Særpreget «samme montør etterpå» peker mot differensiering.")))</f>
         <v/>
       </c>
       <c r="C48" s="21"/>
@@ -1917,7 +1917,7 @@
     </row>
     <row r="50" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="23" t="str">
-        <f aca="false">IF(C49="JA","Hint: Delmålene i kroner: 42 × 51 360 + 215 × 8 830 = 2 157 120 + 1 898 450 = 4 055 570. Hovedmålet: 3 335 640 × 1,20 = 4 002 768. Ekstra dekningsbidrag: 8 flere anlegg × 4 400 + 35 flere ladepunkt × 1 050 = 35 200 + 36 750 = 71 950. Internt er det bedriften selv rår over; eksternt er det som skjer i markedet.","")</f>
+        <f aca="false">IF(C49="JA","Hint: Delmålene i kroner: 30 × 58 060 + 282 × 9 580 = 1 741 800 + 2 701 560 = 4 443 360. Hovedmålet: 3 698 440 × 1,20 = 4 438 128. Ekstra dekningsbidrag: 102 flere ladepunkt × 1 800 − 4 færre anlegg × 11 100 = 183 600 − 44 400 = 139 200. Internt er det bedriften selv rår over; eksternt er det som skjer i markedet.","")</f>
         <v/>
       </c>
       <c r="C50" s="23"/>
@@ -2191,7 +2191,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>77</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
         <v>78</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>106</v>
       </c>
       <c r="C36" s="26" t="str">
-        <f aca="false">IF(E21="","Skriv svaret i cellen E21.",IF(ABS(E21-(78*327.43+14*640+5900))&lt;=2,"Riktig.",IF(ABS(E21-(5900))&lt;=2,"Bare utleggene er med. Egne timer er ikke gratis.",IF(ABS(E21-(78*327.43+5900))&lt;=2,"Montørtimene mangler: 14 × 640 = 8 960.","Ikke riktig ennå. Summen skal være linjene lagt sammen. Rett linjene som ikke er grønne, så stemmer summen."))))</f>
+        <f aca="false">IF(E21="","Skriv svaret i cellen E21.",IF(ABS(E21-(78*327.43+14*640+5900))&lt;=2,"Riktig.",IF(ABS(E21-(5900))&lt;=2,"Bare utleggene er med. Egne timer skal med i budsjettet, regnet med lønnskostnaden.",IF(ABS(E21-(78*327.43+5900))&lt;=2,"Montørtimene mangler: 14 × 640 = 8 960.","Ikke riktig ennå. Summen skal være linjene lagt sammen. Rett linjene som ikke er grønne, så stemmer summen."))))</f>
         <v>Ikke riktig ennå. Summen skal være linjene lagt sammen. Rett linjene som ikke er grønne, så stemmer summen.</v>
       </c>
       <c r="D36" s="26"/>
@@ -2575,7 +2575,7 @@
         <v>108</v>
       </c>
       <c r="G38" s="17" t="str">
-        <f aca="false">IF(C38="","Skriv svaret i den gule cellen.",IF(ABS(C38-(40400/71950*100))&lt;=0.1,"Riktig.",IF(ABS(C38-(40400/3335640*100))&lt;=0.1,"Du har delt på hele omsetningen i fjor. Del på det ekstra dekningsbidraget, 71 950 kr.",IF(ABS(C38-(40400/719930*100))&lt;=0.1,"Du har delt på økningen i omsetning. Planen skal måles mot det ekstra dekningsbidraget, 71 950 kr.",IF(ABS(C38-(71950/40400*100))&lt;=0.1,"Du har delt motsatt vei. Det er planens sum som skal deles på dekningsbidraget.",IF(ABS(C38-(40400/71950))&lt;=0.1,"Du har skrevet brøken. Gang med 100 og svar i prosent.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
+        <f aca="false">IF(C38="","Skriv svaret i den gule cellen.",IF(ABS(C38-(40400/139200*100))&lt;=0.1,"Riktig.",IF(ABS(C38-(40400/3698440*100))&lt;=0.1,"Du har delt på hele omsetningen i fjor. Del på det ekstra dekningsbidraget, 139 200 kr.",IF(ABS(C38-(40400/744920*100))&lt;=0.1,"Du har delt på økningen i omsetning. Planen skal måles mot det ekstra dekningsbidraget, 139 200 kr.",IF(ABS(C38-(139200/40400*100))&lt;=0.1,"Du har delt motsatt vei. Det er planens sum som skal deles på dekningsbidraget.",IF(ABS(C38-(40400/139200))&lt;=0.1,"Du har skrevet brøken. Gang med 100 og svar i prosent.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
         <v>58</v>
       </c>
       <c r="G39" s="17" t="str">
-        <f aca="false">IF(C39="","Skriv svaret i den gule cellen.",IF(ABS(C39-(0.75*71950-40400))&lt;=2,"Riktig.",IF(ABS(C39-(71950-40400))&lt;=2,"Du har brukt hele målet. Nå nås bare 75 %: 0,75 × 71 950.",IF(ABS(C39-(0.75*71950))&lt;=2,"Du har glemt å trekke fra planens sum, 40 400.",IF(ABS(C39-(0.75*40400))&lt;=2,"Du har tatt 75 % av planen. Det er målene som nås 75 %, ikke kostnaden.",IF(ABS(C39-(40400-0.75*71950))&lt;=2,"Snu fortegnet: dekningsbidraget minus planen.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
+        <f aca="false">IF(C39="","Skriv svaret i den gule cellen.",IF(ABS(C39-(0.75*139200-40400))&lt;=2,"Riktig.",IF(ABS(C39-(139200-40400))&lt;=2,"Du har brukt hele målet. Nå nås bare 75 %: 0,75 × 139 200.",IF(ABS(C39-(0.75*139200))&lt;=2,"Du har glemt å trekke fra planens sum, 40 400.",IF(ABS(C39-(0.75*40400))&lt;=2,"Du har tatt 75 % av planen. Det er målene som nås 75 %, ikke kostnaden.",IF(ABS(C39-(40400-0.75*139200))&lt;=2,"Snu fortegnet: dekningsbidraget minus planen.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="53" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="21" t="str">
-        <f aca="false">IF(LEN(B50)&lt;40,"",IF(AND(ISNUMBER(SEARCH("intern",B50)),ISNUMBER(SEARCH("milepæl",B50))),"Bra: du har med både intern markedsføring før ekstern og milepælen som viser avvik i tide. Si gjerne også at 10 270 kr er 14 % av de 71 950 kronene som står på spill.",IF(OR(ISNUMBER(SEARCH("intern",B50)),ISNUMBER(SEARCH("milepæl",B50))),"Du har med noe av det. Oppstartsmøtet er intern markedsføring før den eksterne, og underveisevalueringen er milepælen som gjør at resultatet ikke kommer som en overraskelse.","Tips: oppstartsmøtet er intern markedsføring før ekstern; montørene som møter beboerne, må kjenne kampanjen før brevet går. Underveisevalueringen er milepælen som viser avvik mens det er tid til å justere. 10 270 kr er 14 % av de 71 950 kronene målene gir.")))</f>
+        <f aca="false">IF(LEN(B50)&lt;40,"",IF(AND(ISNUMBER(SEARCH("intern",B50)),ISNUMBER(SEARCH("milepæl",B50))),"Bra: du har med både intern markedsføring før ekstern og milepælen som viser avvik i tide. Si gjerne også at 10 270 kr er 7,4 % av de 139 200 kronene som står på spill.",IF(OR(ISNUMBER(SEARCH("intern",B50)),ISNUMBER(SEARCH("milepæl",B50))),"Du har med noe av det. Oppstartsmøtet er intern markedsføring før den eksterne, og underveisevalueringen er milepælen som gjør at resultatet ikke kommer som en overraskelse.","Tips: oppstartsmøtet er intern markedsføring før ekstern; montørene som møter beboerne, må kjenne kampanjen før brevet går. Underveisevalueringen er milepælen som viser avvik mens det er tid til å justere. 10 270 kr er 7,4 % av de 139 200 kronene målene gir.")))</f>
         <v/>
       </c>
       <c r="C53" s="21"/>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="55" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="23" t="str">
-        <f aca="false">IF(C54="JA","Hint: Hver linje: timer × 327,43 (montørtimer × 640) + utlegg. Brevet: 5 × 327,43 + 1 900 = 3 537. Styrebesøkene: 38,5 × 327,43 + 4 000 = 16 606. Oppstartsmøtet: 14 × 640 = 8 960. Summen er 40 400. a: 40 400 / 71 950 = 56,1 %. b: 0,75 × 71 950 − 40 400 = 13 563.","")</f>
+        <f aca="false">IF(C54="JA","Hint: Hver linje: timer × 327,43 (montørtimer × 640) + utlegg. Brevet: 5 × 327,43 + 1 900 = 3 537. Styrebesøkene: 38,5 × 327,43 + 4 000 = 16 606. Oppstartsmøtet: 14 × 640 = 8 960. Summen er 40 400. a: 40 400 / 139 200 = 29,0 %. b: 0,75 × 139 200 − 40 400 = 64 000.","")</f>
         <v/>
       </c>
       <c r="C55" s="23"/>
@@ -3065,7 +3065,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
         <v>127</v>
       </c>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="C20" s="16"/>
       <c r="G20" s="17" t="str">
-        <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Markedsinntrengning","Riktig. Mer av det samme i markedet avdelingen allerede er i (10.1).","Ikke riktig. Mer av det samme i markedet avdelingen allerede er i (10.1)."))</f>
+        <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Markedsutvikling","Riktig. Samme anlegg til en ny kundegruppe, borettslagene (10.1).","Ikke riktig. Samme anlegg til en ny kundegruppe, borettslagene (10.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z20" s="6" t="s">
@@ -3342,7 +3342,7 @@
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="str">
-        <f aca="false">IF(LEN(B32)&lt;40,"",IF(AND(ISNUMBER(SEARCH("elbil",B32)),ISNUMBER(SEARCH("95",B32))),"Bra: elbilandelen på 95 % er med.",IF(OR(ISNUMBER(SEARCH("elbil",B32)),ISNUMBER(SEARCH("95",B32))),"Du har med noe. Muligheten er at 95 % av nye biler er elbiler: ladepunkt er et modent volummarked.","Tips: 95 % av nye biler i 2025 var elbiler (Opplysningsrådet for veitrafikken). Ladepunkt er et modent volummarked.")))</f>
+        <f aca="false">IF(LEN(B32)&lt;40,"",IF(AND(ISNUMBER(SEARCH("elbil",B32)),ISNUMBER(SEARCH("90",B32))),"Bra: elbilandelen på over 90 % er med.",IF(OR(ISNUMBER(SEARCH("elbil",B32)),ISNUMBER(SEARCH("90",B32))),"Du har med noe. Muligheten er at over 90 % av nye biler er elbiler: ladepunkt er et modent volummarked.","Tips: over 90 % av nye biler i 2025 var elbiler (Opplysningsrådet for veitrafikken). Ladepunkt er et modent volummarked.")))</f>
         <v/>
       </c>
       <c r="C34" s="21"/>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="21" t="str">
-        <f aca="false">IF(LEN(B36)&lt;40,"",IF(AND(ISNUMBER(SEARCH("70",B36)),ISNUMBER(SEARCH("kjede",B36))),"Bra: solmarkedet ned 70 % og kjedene er med.",IF(OR(ISNUMBER(SEARCH("70",B36)),ISNUMBER(SEARCH("kjede",B36))),"Du har med noe. Truslene er at markedet for solkraft på tak falt 70 % i 2026, og at landsdekkende kjeder selger i Oslo øst.","Tips: markedet for solkraft på tak falt rundt 70 % i 2026 (NHO Elektro). Landsdekkende kjeder selger ladepunkt i Oslo øst.")))</f>
+        <f aca="false">IF(LEN(B36)&lt;40,"",IF(AND(ISNUMBER(SEARCH("70",B36)),ISNUMBER(SEARCH("kjede",B36))),"Bra: solmarkedet ned om lag 70 % og kjedene er med.",IF(OR(ISNUMBER(SEARCH("70",B36)),ISNUMBER(SEARCH("kjede",B36))),"Du har med noe. Truslene er at solkraft på tak falt om lag 70 % i første del av 2026, og at landsdekkende kjeder selger i Oslo øst.","Tips: solkraft på tak falt om lag 70 % i første del av 2026 (NHO Elektro, april 2026). Landsdekkende kjeder selger ladepunkt i Oslo øst.")))</f>
         <v/>
       </c>
       <c r="C38" s="21"/>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="21" t="str">
-        <f aca="false">IF(LEN(B46)&lt;40,"",IF(AND(ISNUMBER(SEARCH("20 ladepunkt",B46)),ISNUMBER(SEARCH("juni",B46))),"Bra: antall, frist og avtalen er med.",IF(OR(ISNUMBER(SEARCH("20 ladepunkt",B46)),ISNUMBER(SEARCH("juni",B46))),"Du har med noe. Delmålet skal si minst 20 ladepunkt, innen 30. juni, og hvem som har ansvaret (Kari).","Tips: «Nordlys skal ha signert en rammeavtale med et borettslag om minst 20 ladepunkt innen 30. juni. Ansvar: Kari.»")))</f>
+        <f aca="false">IF(LEN(B46)&lt;40,"",IF(AND(ISNUMBER(SEARCH("20 plasser",B46)),ISNUMBER(SEARCH("juni",B46))),"Bra: antall plasser, frist og kontrakten er med.",IF(OR(ISNUMBER(SEARCH("20 plasser",B46)),ISNUMBER(SEARCH("juni",B46))),"Du har med noe. Delmålet skal si et felles ladeanlegg med minst 20 plasser, innen 30. juni, og hvem som har ansvaret (Kari).","Tips: «Nordlys skal ha signert en kontrakt med et borettslag om et felles ladeanlegg med minst 20 plasser innen 30. juni. Ansvar: Kari.»")))</f>
         <v/>
       </c>
       <c r="C48" s="21"/>
@@ -3618,7 +3618,7 @@
         <v>58</v>
       </c>
       <c r="G58" s="17" t="str">
-        <f aca="false">IF(C58="","Skriv svaret i den gule cellen.",IF(ABS(C58-(78*327.43+14*640+5900))&lt;=1,"Riktig.",IF(ABS(C58-(5900))&lt;=1,"Bare utleggene er med. Egne timer er ikke gratis.",IF(ABS(C58-(78*327.43+5900))&lt;=1,"Montørtimene mangler: 14 × 640 = 8 960.",IF(ABS(C58-(92*327.43+5900))&lt;=1,"Du har brukt 327,43 på alle timene. Montørtimene koster 640 kr.",IF(ABS(C58-(92*640+5900))&lt;=1,"Du har brukt 640 på alle timene. Administrasjonstimene koster 327,43 kr.",IF(ABS(C58-(78*327.43+14*640))&lt;=1,"Utleggene på 5 900 kr mangler.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))))</f>
+        <f aca="false">IF(C58="","Skriv svaret i den gule cellen.",IF(ABS(C58-(78*327.43+14*640+5900))&lt;=1,"Riktig.",IF(ABS(C58-(5900))&lt;=1,"Bare utleggene er med. Egne timer skal med i budsjettet, regnet med lønnskostnaden.",IF(ABS(C58-(78*327.43+5900))&lt;=1,"Montørtimene mangler: 14 × 640 = 8 960.",IF(ABS(C58-(92*327.43+5900))&lt;=1,"Du har brukt 327,43 på alle timene. Montørtimene koster 640 kr.",IF(ABS(C58-(92*640+5900))&lt;=1,"Du har brukt 640 på alle timene. Administrasjonstimene koster 327,43 kr.",IF(ABS(C58-(78*327.43+14*640))&lt;=1,"Utleggene på 5 900 kr mangler.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="C66" s="16"/>
       <c r="G66" s="17" t="str">
-        <f aca="false">IF(C66="","Velg i nedtrekksmenyen.",IF(C66="Målet nådd innenfor rammen","Riktig. Avtalen kom, og planen kostet mindre enn rammen. Evaluer prosessen: hva virket?","Ikke riktig. Avtalen kom, og planen kostet mindre enn rammen. Evaluer prosessen: hva virket?"))</f>
+        <f aca="false">IF(C66="","Velg i nedtrekksmenyen.",IF(C66="Målet nådd innenfor rammen","Riktig. Kontrakten kom, og planen kostet mindre enn rammen. Evaluer prosessen: hva virket?","Ikke riktig. Kontrakten kom, og planen kostet mindre enn rammen. Evaluer prosessen: hva virket?"))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="C67" s="16"/>
       <c r="G67" s="17" t="str">
-        <f aca="false">IF(C67="","Velg i nedtrekksmenyen.",IF(C67="Målet nådd, men rammen sprakk","Riktig. Avtalen kom, men 5 600 kr over rammen. Hvilke linjer ble dyrere? Ofte timene.","Ikke riktig. Avtalen kom, men 5 600 kr over rammen. Hvilke linjer ble dyrere? Ofte timene."))</f>
+        <f aca="false">IF(C67="","Velg i nedtrekksmenyen.",IF(C67="Målet nådd, men rammen sprakk","Riktig. Kontrakten kom, men 5 600 kr over rammen. Hvilke linjer ble dyrere? Ofte timene.","Ikke riktig. Kontrakten kom, men 5 600 kr over rammen. Hvilke linjer ble dyrere? Ofte timene."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="30" t="s">
         <v>178</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>180</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>4055570</v>
+        <v>4443360</v>
       </c>
       <c r="D8" s="30" t="s">
         <v>181</v>
@@ -4081,7 +4081,7 @@
         <v>182</v>
       </c>
       <c r="C9" s="14" t="n">
-        <v>4002768</v>
+        <v>4438128</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>183</v>
@@ -4092,7 +4092,7 @@
         <v>184</v>
       </c>
       <c r="C10" s="14" t="n">
-        <v>71950</v>
+        <v>139200</v>
       </c>
       <c r="D10" s="30" t="s">
         <v>185</v>
@@ -4141,7 +4141,7 @@
         <v>194</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>56.1</v>
+        <v>29</v>
       </c>
       <c r="D15" s="30" t="s">
         <v>195</v>
@@ -4152,7 +4152,7 @@
         <v>196</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>13563</v>
+        <v>64000</v>
       </c>
       <c r="D16" s="30" t="s">
         <v>197</v>
@@ -4185,7 +4185,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="30" t="s">
         <v>204</v>
       </c>

--- a/pensum/ma10/MA10_Markedsplanen_oppsummert_Oppgaver_v6.xlsx
+++ b/pensum/ma10/MA10_Markedsplanen_oppsummert_Oppgaver_v6.xlsx
@@ -871,7 +871,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -994,6 +994,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1281,7 +1285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1306,27 +1310,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1563,7 +1567,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
         <v>40</v>
       </c>
@@ -1594,7 +1598,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="9" t="s">
         <v>42</v>
       </c>
@@ -1612,7 +1616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="8" t="s">
         <v>43</v>
       </c>
@@ -1625,7 +1629,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="15" t="s">
         <v>44</v>
       </c>
@@ -1638,7 +1642,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="15" t="s">
         <v>45</v>
       </c>
@@ -1656,7 +1660,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="8" t="s">
         <v>46</v>
       </c>
@@ -1752,7 +1756,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="34" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="8" t="s">
         <v>55</v>
       </c>
@@ -1797,7 +1801,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="15" t="s">
         <v>62</v>
       </c>
@@ -1818,7 +1822,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="39" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="8" t="s">
         <v>65</v>
       </c>
@@ -1831,7 +1835,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="40" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="15" t="s">
         <v>67</v>
       </c>
@@ -1854,7 +1858,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="42" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="15" t="s">
         <v>70</v>
       </c>
@@ -2305,8 +2309,8 @@
       </c>
       <c r="E13" s="18"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="31" r="B14" t="s">
         <v>87</v>
       </c>
       <c r="C14" s="24" t="n">
@@ -2353,8 +2357,8 @@
       </c>
       <c r="E17" s="18"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="31" r="B18" t="s">
         <v>91</v>
       </c>
       <c r="C18" s="24" t="n">
@@ -2416,7 +2420,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="9" t="s">
         <v>95</v>
       </c>
@@ -2426,7 +2430,7 @@
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="8" t="s">
         <v>96</v>
       </c>
@@ -2566,7 +2570,7 @@
       <c r="F36" s="26"/>
       <c r="G36" s="26"/>
     </row>
-    <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="38" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="15" t="s">
         <v>107</v>
       </c>
@@ -2592,7 +2596,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="41" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="8" t="s">
         <v>110</v>
       </c>
@@ -3096,7 +3100,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="105" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="9" t="s">
         <v>128</v>
       </c>
@@ -3114,7 +3118,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="8" t="s">
         <v>129</v>
       </c>
@@ -3127,7 +3131,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="9" t="s">
         <v>130</v>
       </c>
@@ -3194,7 +3198,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="8" t="s">
         <v>132</v>
       </c>
@@ -3207,7 +3211,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="9" t="s">
         <v>133</v>
       </c>
@@ -3256,7 +3260,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="9" t="s">
         <v>134</v>
       </c>
@@ -3305,7 +3309,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="9" t="s">
         <v>136</v>
       </c>
@@ -3354,7 +3358,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="35" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="9" t="s">
         <v>141</v>
       </c>
@@ -3408,7 +3412,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="40" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="8" t="s">
         <v>147</v>
       </c>
@@ -3421,7 +3425,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="41" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="9" t="s">
         <v>149</v>
       </c>
@@ -3470,7 +3474,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="45" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="9" t="s">
         <v>152</v>
       </c>
@@ -3524,7 +3528,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="50" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="8" t="s">
         <v>153</v>
       </c>
@@ -3599,7 +3603,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="57" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="8" t="s">
         <v>159</v>
       </c>
@@ -3609,7 +3613,7 @@
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="58" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="15" t="s">
         <v>160</v>
       </c>
@@ -3622,7 +3626,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="60" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="8" t="s">
         <v>161</v>
       </c>
@@ -3652,7 +3656,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="64" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="8" t="s">
         <v>164</v>
       </c>
@@ -3712,7 +3716,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="71" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="9" t="s">
         <v>170</v>
       </c>
